--- a/gstdatabase/Gross_Net_Tax_collection.xlsx
+++ b/gstdatabase/Gross_Net_Tax_collection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16A534A-2E33-4824-B448-6F53DF92F847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CAADC9-1616-4F05-999F-DC8E0FDBE957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="14" activeTab="22" xr2:uid="{5CAD827C-DDF4-9F48-BEDE-38002A84F822}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="17" activeTab="25" xr2:uid="{5CAD827C-DDF4-9F48-BEDE-38002A84F822}"/>
   </bookViews>
   <sheets>
     <sheet name="Apr-24" sheetId="2" r:id="rId1"/>
@@ -36,6 +36,9 @@
     <sheet name="Dec-25" sheetId="22" r:id="rId21"/>
     <sheet name="Jan-26" sheetId="23" r:id="rId22"/>
     <sheet name="Feb-26" sheetId="24" r:id="rId23"/>
+    <sheet name="Mar_26" sheetId="25" r:id="rId24"/>
+    <sheet name="Apr-26" sheetId="26" r:id="rId25"/>
+    <sheet name="May-26" sheetId="27" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Apr-24'!$A$1:$G$52</definedName>
@@ -51,6 +54,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="15">'Jul-25'!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Jun-24'!$A$1:$G$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'Jun-25'!$A$1:$G$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="23">Mar_26!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'Mar-25'!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'May-24'!$A$1:$G$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'May-25'!$A$1:$G$53</definedName>
@@ -82,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="138">
   <si>
     <t>Monthly</t>
   </si>
@@ -458,6 +462,45 @@
   <si>
     <t>Feb-25</t>
   </si>
+  <si>
+    <t xml:space="preserve">GST Gross and Net Collections as on  31/03/2026 (Amount in crores) </t>
+  </si>
+  <si>
+    <t>Mar-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GST Gross and Net Collections as on  30/4/2026 (Amount in crores) </t>
+  </si>
+  <si>
+    <t>Apr-25</t>
+  </si>
+  <si>
+    <t>D.1 Cess*</t>
+  </si>
+  <si>
+    <t>Domestic</t>
+  </si>
+  <si>
+    <t>Import</t>
+  </si>
+  <si>
+    <t>Refund</t>
+  </si>
+  <si>
+    <t>Net Cess Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GST Gross and Net Collections as on  5/31/2026 (Amount in crores) </t>
+  </si>
+  <si>
+    <t>May  25</t>
+  </si>
+  <si>
+    <t>D = C/B</t>
+  </si>
+  <si>
+    <t>G = F/E</t>
+  </si>
 </sst>
 </file>
 
@@ -470,7 +513,7 @@
     <numFmt numFmtId="167" formatCode="mmm\-yyyy"/>
     <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -742,6 +785,19 @@
       <color rgb="FF000000"/>
       <name val="Aptos"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="39">
@@ -1186,7 +1242,7 @@
     <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1475,6 +1531,37 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1484,13 +1571,10 @@
     <xf numFmtId="0" fontId="33" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1533,16 +1617,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1913,28 +1997,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="172" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="163"/>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="163"/>
-      <c r="F1" s="163"/>
-      <c r="G1" s="164"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="174"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -3066,15 +3150,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="166" t="s">
+      <c r="A55" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="166"/>
-      <c r="C55" s="166"/>
-      <c r="D55" s="166"/>
-      <c r="E55" s="166"/>
-      <c r="F55" s="166"/>
-      <c r="G55" s="166"/>
+      <c r="B55" s="176"/>
+      <c r="C55" s="176"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3108,36 +3192,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="180" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="168"/>
-      <c r="H1" s="168"/>
-      <c r="I1" s="168"/>
-      <c r="J1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="179"/>
     </row>
     <row r="2" spans="1:12" ht="15.6">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="165" t="s">
+      <c r="C2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165" t="s">
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175" t="s">
         <v>78</v>
       </c>
-      <c r="H2" s="165"/>
-      <c r="I2" s="165"/>
-      <c r="J2" s="165"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="175"/>
+      <c r="J2" s="175"/>
     </row>
     <row r="3" spans="1:12" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -4730,33 +4814,33 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="18">
-      <c r="A54" s="172" t="s">
+      <c r="A54" s="182" t="s">
         <v>85</v>
       </c>
-      <c r="B54" s="172"/>
-      <c r="C54" s="172"/>
-      <c r="D54" s="172"/>
+      <c r="B54" s="182"/>
+      <c r="C54" s="182"/>
+      <c r="D54" s="182"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="173" t="s">
+      <c r="A55" s="183" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="173"/>
-      <c r="C55" s="173"/>
-      <c r="D55" s="173"/>
+      <c r="B55" s="183"/>
+      <c r="C55" s="183"/>
+      <c r="D55" s="183"/>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="B56" s="174" t="s">
+      <c r="B56" s="184" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="174"/>
-      <c r="D56" s="174"/>
+      <c r="C56" s="184"/>
+      <c r="D56" s="184"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="171" t="s">
+      <c r="A57" s="181" t="s">
         <v>88</v>
       </c>
       <c r="B57" s="100" t="s">
@@ -4765,19 +4849,19 @@
       <c r="C57" s="100" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="171" t="s">
+      <c r="D57" s="181" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="171"/>
+      <c r="A58" s="181"/>
       <c r="B58" s="100" t="s">
         <v>91</v>
       </c>
       <c r="C58" s="100" t="s">
         <v>91</v>
       </c>
-      <c r="D58" s="171"/>
+      <c r="D58" s="181"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="101" t="s">
@@ -4928,28 +5012,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="180" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -5948,28 +6032,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="167" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="158"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -7010,28 +7094,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.6">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="185" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:13" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:13" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -8081,28 +8165,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="167" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="158"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="157"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="177" t="s">
+      <c r="C2" s="168"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="157"/>
-      <c r="G2" s="158"/>
+      <c r="F2" s="168"/>
+      <c r="G2" s="169"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -9137,28 +9221,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="167" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="158"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -10157,28 +10241,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="167" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="158"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -11184,28 +11268,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="167" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="158"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -12250,28 +12334,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="167" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="158"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="177" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="157"/>
-      <c r="G2" s="158"/>
+      <c r="F2" s="168"/>
+      <c r="G2" s="169"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -13317,28 +13401,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="158"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="177" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="157"/>
-      <c r="G2" s="158"/>
+      <c r="F2" s="168"/>
+      <c r="G2" s="169"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -14373,28 +14457,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="172" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="163"/>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="163"/>
-      <c r="F1" s="163"/>
-      <c r="G1" s="164"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="174"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -15489,15 +15573,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="166" t="s">
+      <c r="A55" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="166"/>
-      <c r="C55" s="166"/>
-      <c r="D55" s="166"/>
-      <c r="E55" s="166"/>
-      <c r="F55" s="166"/>
-      <c r="G55" s="166"/>
+      <c r="B55" s="176"/>
+      <c r="C55" s="176"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -15529,28 +15613,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="158"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="186" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="160"/>
-      <c r="D2" s="161"/>
-      <c r="E2" s="159" t="s">
+      <c r="C2" s="187"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="186" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="160"/>
-      <c r="G2" s="161"/>
+      <c r="F2" s="187"/>
+      <c r="G2" s="188"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -16596,28 +16680,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="167" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="158"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -17643,28 +17727,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="167" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="158"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -18705,28 +18789,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="167" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="158"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -19218,7 +19302,7 @@
       <c r="B29" s="67">
         <v>10004.94</v>
       </c>
-      <c r="C29" s="178">
+      <c r="C29" s="156">
         <v>12656.20707</v>
       </c>
       <c r="D29" s="11"/>
@@ -19239,7 +19323,7 @@
       <c r="B30" s="67">
         <v>117.56</v>
       </c>
-      <c r="C30" s="178">
+      <c r="C30" s="156">
         <v>4.7895927</v>
       </c>
       <c r="D30" s="11"/>
@@ -19746,6 +19830,2973 @@
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="82" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF3D342-27CB-4B13-AE0D-697BAB6F677E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="38.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="6" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1"/>
+    <col min="9" max="10" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.6">
+      <c r="A1" s="167" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.6">
+      <c r="A2" s="108"/>
+      <c r="B2" s="170" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.6">
+      <c r="A3" s="109" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="110" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="111">
+        <v>46082</v>
+      </c>
+      <c r="D3" s="109" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="110" t="s">
+        <v>126</v>
+      </c>
+      <c r="F3" s="111">
+        <v>46082</v>
+      </c>
+      <c r="G3" s="109" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.6">
+      <c r="A4" s="109" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="111" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="109" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="109" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="109" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" collapsed="1">
+      <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="159" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="160" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="157" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="157" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="161" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" outlineLevel="1">
+      <c r="A6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="77">
+        <v>38144.511200000001</v>
+      </c>
+      <c r="C6" s="34">
+        <v>40549.089999999997</v>
+      </c>
+      <c r="D6" s="104"/>
+      <c r="E6" s="34">
+        <v>413775.79</v>
+      </c>
+      <c r="F6" s="34">
+        <v>444309.47</v>
+      </c>
+      <c r="G6" s="80"/>
+      <c r="H6" s="13"/>
+    </row>
+    <row r="7" spans="1:8" outlineLevel="1">
+      <c r="A7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="77">
+        <v>49890.794000000002</v>
+      </c>
+      <c r="C7" s="34">
+        <v>53268.31</v>
+      </c>
+      <c r="D7" s="104"/>
+      <c r="E7" s="34">
+        <v>516447.5</v>
+      </c>
+      <c r="F7" s="34">
+        <v>551301.61</v>
+      </c>
+      <c r="G7" s="80"/>
+    </row>
+    <row r="8" spans="1:8" outlineLevel="1">
+      <c r="A8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="77">
+        <v>50071.002399999998</v>
+      </c>
+      <c r="C8" s="34">
+        <v>52384.86</v>
+      </c>
+      <c r="D8" s="104"/>
+      <c r="E8" s="34">
+        <v>603581.56999999995</v>
+      </c>
+      <c r="F8" s="34">
+        <v>636158.30000000005</v>
+      </c>
+      <c r="G8" s="80"/>
+      <c r="H8" s="13"/>
+    </row>
+    <row r="9" spans="1:8" outlineLevel="1">
+      <c r="A9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="77">
+        <v>11115.8642</v>
+      </c>
+      <c r="C9" s="34">
+        <v>103.26</v>
+      </c>
+      <c r="D9" s="104"/>
+      <c r="E9" s="34">
+        <v>141891.71</v>
+      </c>
+      <c r="F9" s="34">
+        <v>98708.19</v>
+      </c>
+      <c r="G9" s="80"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="118">
+        <v>149222.17180000001</v>
+      </c>
+      <c r="C10" s="35">
+        <v>146305.52000000002</v>
+      </c>
+      <c r="D10" s="61">
+        <v>-1.9545622446424549E-2</v>
+      </c>
+      <c r="E10" s="73">
+        <v>1675696.5699999998</v>
+      </c>
+      <c r="F10" s="73">
+        <v>1730477.5699999998</v>
+      </c>
+      <c r="G10" s="61">
+        <v>3.2691479460389417E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="14"/>
+      <c r="B11" s="118"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="61"/>
+    </row>
+    <row r="12" spans="1:8" ht="12.75" customHeight="1" collapsed="1">
+      <c r="A12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="104"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="61"/>
+    </row>
+    <row r="13" spans="1:8" outlineLevel="1">
+      <c r="A13" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="77">
+        <v>45738.611562099999</v>
+      </c>
+      <c r="C13" s="77">
+        <v>53861.432642450003</v>
+      </c>
+      <c r="D13" s="104"/>
+      <c r="E13" s="34">
+        <v>521709.86156210001</v>
+      </c>
+      <c r="F13" s="34">
+        <v>595326.84089454997</v>
+      </c>
+      <c r="G13" s="80"/>
+    </row>
+    <row r="14" spans="1:8" outlineLevel="1">
+      <c r="A14" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="77">
+        <v>1136.6545821</v>
+      </c>
+      <c r="C14" s="77">
+        <v>2.6953400000000002E-2</v>
+      </c>
+      <c r="D14" s="104"/>
+      <c r="E14" s="34">
+        <v>11410.8445821</v>
+      </c>
+      <c r="F14" s="34">
+        <v>6014.7873476000004</v>
+      </c>
+      <c r="G14" s="80"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="35">
+        <v>46875.266144199995</v>
+      </c>
+      <c r="C15" s="35">
+        <v>53861.459595850007</v>
+      </c>
+      <c r="D15" s="61">
+        <v>0.14903794743604748</v>
+      </c>
+      <c r="E15" s="35">
+        <v>533120.70614420006</v>
+      </c>
+      <c r="F15" s="35">
+        <v>601341.62824214995</v>
+      </c>
+      <c r="G15" s="63">
+        <v>0.12796524560330491</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="61"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.6">
+      <c r="A17" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="75">
+        <v>38144.511200000001</v>
+      </c>
+      <c r="C17" s="65">
+        <v>40549.089999999997</v>
+      </c>
+      <c r="D17" s="76"/>
+      <c r="E17" s="65">
+        <v>413775.79</v>
+      </c>
+      <c r="F17" s="65">
+        <v>444309.47</v>
+      </c>
+      <c r="G17" s="76"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.6">
+      <c r="A18" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="75">
+        <v>49890.794000000002</v>
+      </c>
+      <c r="C18" s="65">
+        <v>53268.31</v>
+      </c>
+      <c r="D18" s="76"/>
+      <c r="E18" s="65">
+        <v>516447.5</v>
+      </c>
+      <c r="F18" s="65">
+        <v>551301.61</v>
+      </c>
+      <c r="G18" s="76"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.6">
+      <c r="A19" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="75">
+        <v>95809.613962100004</v>
+      </c>
+      <c r="C19" s="65">
+        <v>106246.29264245</v>
+      </c>
+      <c r="D19" s="76"/>
+      <c r="E19" s="65">
+        <v>1125291.4315621001</v>
+      </c>
+      <c r="F19" s="65">
+        <v>1231485.1408945499</v>
+      </c>
+      <c r="G19" s="76"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.6">
+      <c r="A20" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="75">
+        <v>12252.5187821</v>
+      </c>
+      <c r="C20" s="65">
+        <v>103.2869534</v>
+      </c>
+      <c r="D20" s="76"/>
+      <c r="E20" s="65">
+        <v>153302.55458209998</v>
+      </c>
+      <c r="F20" s="65">
+        <v>104722.9773476</v>
+      </c>
+      <c r="G20" s="76"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.6">
+      <c r="A21" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="40">
+        <v>196097.43794420001</v>
+      </c>
+      <c r="C21" s="40">
+        <v>200166.97959584999</v>
+      </c>
+      <c r="D21" s="66">
+        <v>2.0752712218963243E-2</v>
+      </c>
+      <c r="E21" s="40">
+        <v>2208817.2761442</v>
+      </c>
+      <c r="F21" s="40">
+        <v>2331819.1982421498</v>
+      </c>
+      <c r="G21" s="66">
+        <v>5.5686780172539585E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="20" customFormat="1" collapsed="1">
+      <c r="A22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="34"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="107"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="104"/>
+    </row>
+    <row r="23" spans="1:8" s="20" customFormat="1" outlineLevel="1">
+      <c r="A23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="77">
+        <v>2620.0700000000002</v>
+      </c>
+      <c r="C23" s="77">
+        <v>3595.05</v>
+      </c>
+      <c r="D23" s="104"/>
+      <c r="E23" s="59">
+        <v>33492.54</v>
+      </c>
+      <c r="F23" s="59">
+        <v>38700.61</v>
+      </c>
+      <c r="G23" s="80"/>
+    </row>
+    <row r="24" spans="1:8" s="20" customFormat="1" outlineLevel="1">
+      <c r="A24" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="77">
+        <v>3659.76</v>
+      </c>
+      <c r="C24" s="77">
+        <v>4642.55</v>
+      </c>
+      <c r="D24" s="104"/>
+      <c r="E24" s="59">
+        <v>42635.39</v>
+      </c>
+      <c r="F24" s="59">
+        <v>49393.31</v>
+      </c>
+      <c r="G24" s="80"/>
+    </row>
+    <row r="25" spans="1:8" s="20" customFormat="1" outlineLevel="1">
+      <c r="A25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="77">
+        <v>5049.1499999999996</v>
+      </c>
+      <c r="C25" s="77">
+        <v>6621.93</v>
+      </c>
+      <c r="D25" s="104"/>
+      <c r="E25" s="59">
+        <v>56111.94</v>
+      </c>
+      <c r="F25" s="59">
+        <v>75667.790000000008</v>
+      </c>
+      <c r="G25" s="80"/>
+    </row>
+    <row r="26" spans="1:8" s="20" customFormat="1" outlineLevel="1">
+      <c r="A26" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="77">
+        <v>192.13</v>
+      </c>
+      <c r="C26" s="77">
+        <v>253.63</v>
+      </c>
+      <c r="D26" s="104"/>
+      <c r="E26" s="59">
+        <v>2912.38</v>
+      </c>
+      <c r="F26" s="59">
+        <v>4426.07</v>
+      </c>
+      <c r="G26" s="80"/>
+    </row>
+    <row r="27" spans="1:8" s="20" customFormat="1">
+      <c r="A27" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" s="78">
+        <v>11521.109999999999</v>
+      </c>
+      <c r="C27" s="35">
+        <v>15113.16</v>
+      </c>
+      <c r="D27" s="63">
+        <v>0.31177985454526524</v>
+      </c>
+      <c r="E27" s="35">
+        <v>135152.25</v>
+      </c>
+      <c r="F27" s="35">
+        <v>168187.78000000003</v>
+      </c>
+      <c r="G27" s="63">
+        <v>0.24443196469167194</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="20" customFormat="1" collapsed="1">
+      <c r="A28" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="104"/>
+    </row>
+    <row r="29" spans="1:8" s="20" customFormat="1" outlineLevel="1">
+      <c r="A29" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="77">
+        <v>8071.17</v>
+      </c>
+      <c r="C29" s="77">
+        <v>7214.0167400999999</v>
+      </c>
+      <c r="D29" s="104"/>
+      <c r="E29" s="34">
+        <v>115978.54244670001</v>
+      </c>
+      <c r="F29" s="34">
+        <v>128568.44251160001</v>
+      </c>
+      <c r="G29" s="80"/>
+      <c r="H29" s="21"/>
+    </row>
+    <row r="30" spans="1:8" s="20" customFormat="1" outlineLevel="1">
+      <c r="A30" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="77">
+        <v>17.54</v>
+      </c>
+      <c r="C30" s="77">
+        <v>26.209059799999999</v>
+      </c>
+      <c r="D30" s="104"/>
+      <c r="E30" s="34">
+        <v>1691.0055373999999</v>
+      </c>
+      <c r="F30" s="34">
+        <v>1258.3026131999998</v>
+      </c>
+      <c r="G30" s="80"/>
+      <c r="H30" s="21"/>
+    </row>
+    <row r="31" spans="1:8" s="20" customFormat="1">
+      <c r="A31" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="35">
+        <v>8088.71</v>
+      </c>
+      <c r="C31" s="35">
+        <v>7240.2257999000003</v>
+      </c>
+      <c r="D31" s="63">
+        <v>-0.10489549645601182</v>
+      </c>
+      <c r="E31" s="35">
+        <v>117669.54798410001</v>
+      </c>
+      <c r="F31" s="35">
+        <v>129826.7451248</v>
+      </c>
+      <c r="G31" s="63">
+        <v>0.10331642594856172</v>
+      </c>
+      <c r="H31" s="21"/>
+    </row>
+    <row r="32" spans="1:8" s="20" customFormat="1">
+      <c r="A32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="21"/>
+    </row>
+    <row r="33" spans="1:8" s="20" customFormat="1">
+      <c r="A33" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="42">
+        <v>2620.0700000000002</v>
+      </c>
+      <c r="C33" s="42">
+        <v>3595.05</v>
+      </c>
+      <c r="D33" s="82"/>
+      <c r="E33" s="42">
+        <v>33492.54</v>
+      </c>
+      <c r="F33" s="42">
+        <v>38700.61</v>
+      </c>
+      <c r="G33" s="63"/>
+      <c r="H33" s="21"/>
+    </row>
+    <row r="34" spans="1:8" s="20" customFormat="1">
+      <c r="A34" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="42">
+        <v>3659.76</v>
+      </c>
+      <c r="C34" s="42">
+        <v>4642.55</v>
+      </c>
+      <c r="D34" s="82"/>
+      <c r="E34" s="42">
+        <v>42635.39</v>
+      </c>
+      <c r="F34" s="42">
+        <v>49393.31</v>
+      </c>
+      <c r="G34" s="63"/>
+      <c r="H34" s="21"/>
+    </row>
+    <row r="35" spans="1:8" s="20" customFormat="1">
+      <c r="A35" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="42">
+        <v>13120.32</v>
+      </c>
+      <c r="C35" s="42">
+        <v>13835.9467401</v>
+      </c>
+      <c r="D35" s="82"/>
+      <c r="E35" s="42">
+        <v>172090.48244670001</v>
+      </c>
+      <c r="F35" s="42">
+        <v>204236.23251160001</v>
+      </c>
+      <c r="G35" s="63"/>
+      <c r="H35" s="21"/>
+    </row>
+    <row r="36" spans="1:8" s="20" customFormat="1">
+      <c r="A36" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="42">
+        <v>209.67</v>
+      </c>
+      <c r="C36" s="42">
+        <v>279.83905979999997</v>
+      </c>
+      <c r="D36" s="82"/>
+      <c r="E36" s="42">
+        <v>4603.3855373999995</v>
+      </c>
+      <c r="F36" s="42">
+        <v>5684.3726131999993</v>
+      </c>
+      <c r="G36" s="63"/>
+      <c r="H36" s="21"/>
+    </row>
+    <row r="37" spans="1:8" s="20" customFormat="1" ht="15.6">
+      <c r="A37" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="40">
+        <v>19609.82</v>
+      </c>
+      <c r="C37" s="40">
+        <v>22353.385799899999</v>
+      </c>
+      <c r="D37" s="66">
+        <v>0.13990872110440411</v>
+      </c>
+      <c r="E37" s="40">
+        <v>252821.79798410001</v>
+      </c>
+      <c r="F37" s="40">
+        <v>298014.52512479998</v>
+      </c>
+      <c r="G37" s="66">
+        <v>0.1787532859154104</v>
+      </c>
+      <c r="H37" s="21"/>
+    </row>
+    <row r="38" spans="1:8" s="20" customFormat="1">
+      <c r="A38" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="35"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="21"/>
+    </row>
+    <row r="39" spans="1:8" s="20" customFormat="1">
+      <c r="A39" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="42">
+        <v>35524.441200000001</v>
+      </c>
+      <c r="C39" s="42">
+        <v>36954.039999999994</v>
+      </c>
+      <c r="D39" s="82">
+        <v>0</v>
+      </c>
+      <c r="E39" s="42">
+        <v>380283.25</v>
+      </c>
+      <c r="F39" s="42">
+        <v>405608.86</v>
+      </c>
+      <c r="G39" s="82"/>
+      <c r="H39" s="21"/>
+    </row>
+    <row r="40" spans="1:8" s="20" customFormat="1">
+      <c r="A40" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="42">
+        <v>46231.034</v>
+      </c>
+      <c r="C40" s="42">
+        <v>48625.759999999995</v>
+      </c>
+      <c r="D40" s="82">
+        <v>0</v>
+      </c>
+      <c r="E40" s="42">
+        <v>473812.11</v>
+      </c>
+      <c r="F40" s="42">
+        <v>501908.3</v>
+      </c>
+      <c r="G40" s="82"/>
+      <c r="H40" s="21"/>
+    </row>
+    <row r="41" spans="1:8" s="20" customFormat="1">
+      <c r="A41" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="42">
+        <v>45021.852399999996</v>
+      </c>
+      <c r="C41" s="42">
+        <v>45762.93</v>
+      </c>
+      <c r="D41" s="82">
+        <v>0</v>
+      </c>
+      <c r="E41" s="42">
+        <v>547469.62999999989</v>
+      </c>
+      <c r="F41" s="42">
+        <v>560490.51</v>
+      </c>
+      <c r="G41" s="82"/>
+      <c r="H41" s="21"/>
+    </row>
+    <row r="42" spans="1:8" s="20" customFormat="1">
+      <c r="A42" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="42">
+        <v>10923.734200000001</v>
+      </c>
+      <c r="C42" s="42">
+        <v>-150.37</v>
+      </c>
+      <c r="D42" s="82">
+        <v>0</v>
+      </c>
+      <c r="E42" s="42">
+        <v>138979.32999999999</v>
+      </c>
+      <c r="F42" s="42">
+        <v>94282.12</v>
+      </c>
+      <c r="G42" s="82"/>
+      <c r="H42" s="21"/>
+    </row>
+    <row r="43" spans="1:8" s="20" customFormat="1">
+      <c r="A43" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43" s="43">
+        <v>137701.0618</v>
+      </c>
+      <c r="C43" s="43">
+        <v>131192.35999999999</v>
+      </c>
+      <c r="D43" s="63">
+        <v>-4.726681459582216E-2</v>
+      </c>
+      <c r="E43" s="43">
+        <v>1540544.3199999998</v>
+      </c>
+      <c r="F43" s="43">
+        <v>1562289.79</v>
+      </c>
+      <c r="G43" s="63">
+        <v>1.4115445896421885E-2</v>
+      </c>
+      <c r="H43" s="21"/>
+    </row>
+    <row r="44" spans="1:8" s="20" customFormat="1">
+      <c r="A44" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" s="35"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="61"/>
+      <c r="H44" s="21"/>
+    </row>
+    <row r="45" spans="1:8" s="20" customFormat="1">
+      <c r="A45" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="42">
+        <v>37667.441562100001</v>
+      </c>
+      <c r="C45" s="42">
+        <v>46647.415902350003</v>
+      </c>
+      <c r="D45" s="82">
+        <v>0</v>
+      </c>
+      <c r="E45" s="42">
+        <v>405731.31911539997</v>
+      </c>
+      <c r="F45" s="42">
+        <v>466758.39838294999</v>
+      </c>
+      <c r="G45" s="82"/>
+      <c r="H45" s="21"/>
+    </row>
+    <row r="46" spans="1:8" s="20" customFormat="1">
+      <c r="A46" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="42">
+        <v>1119.1145821</v>
+      </c>
+      <c r="C46" s="42">
+        <v>-26.182106399999999</v>
+      </c>
+      <c r="D46" s="82">
+        <v>0</v>
+      </c>
+      <c r="E46" s="42">
+        <v>9719.8390447000002</v>
+      </c>
+      <c r="F46" s="42">
+        <v>4756.4847344000009</v>
+      </c>
+      <c r="G46" s="82"/>
+      <c r="H46" s="21"/>
+    </row>
+    <row r="47" spans="1:8" s="20" customFormat="1">
+      <c r="A47" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="43">
+        <v>38786.556144200003</v>
+      </c>
+      <c r="C47" s="43">
+        <v>46621.23379595</v>
+      </c>
+      <c r="D47" s="63">
+        <v>0.20199415355048478</v>
+      </c>
+      <c r="E47" s="43">
+        <v>415451.15816009999</v>
+      </c>
+      <c r="F47" s="43">
+        <v>471514.88311734999</v>
+      </c>
+      <c r="G47" s="63">
+        <v>0.13494660889992049</v>
+      </c>
+      <c r="H47" s="21"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" s="35"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="61"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="35"/>
+      <c r="G48" s="61"/>
+    </row>
+    <row r="49" spans="1:7" ht="15.6">
+      <c r="A49" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="65">
+        <v>35524.441200000001</v>
+      </c>
+      <c r="C49" s="65">
+        <v>36954.039999999994</v>
+      </c>
+      <c r="D49" s="76"/>
+      <c r="E49" s="65">
+        <v>380283.25</v>
+      </c>
+      <c r="F49" s="65">
+        <v>405608.86</v>
+      </c>
+      <c r="G49" s="76"/>
+    </row>
+    <row r="50" spans="1:7" ht="15.6">
+      <c r="A50" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" s="65">
+        <v>46231.034</v>
+      </c>
+      <c r="C50" s="65">
+        <v>48625.759999999995</v>
+      </c>
+      <c r="D50" s="76"/>
+      <c r="E50" s="65">
+        <v>473812.11</v>
+      </c>
+      <c r="F50" s="65">
+        <v>501908.3</v>
+      </c>
+      <c r="G50" s="76"/>
+    </row>
+    <row r="51" spans="1:7" ht="15.6">
+      <c r="A51" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="65">
+        <v>82689.293962099997</v>
+      </c>
+      <c r="C51" s="65">
+        <v>92410.345902350004</v>
+      </c>
+      <c r="D51" s="76"/>
+      <c r="E51" s="65">
+        <v>953200.94911539985</v>
+      </c>
+      <c r="F51" s="65">
+        <v>1027248.90838295</v>
+      </c>
+      <c r="G51" s="76"/>
+    </row>
+    <row r="52" spans="1:7" ht="15.6">
+      <c r="A52" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="65">
+        <v>12042.848782100002</v>
+      </c>
+      <c r="C52" s="65">
+        <v>-176.55210640000001</v>
+      </c>
+      <c r="D52" s="76"/>
+      <c r="E52" s="65">
+        <v>148699.16904469999</v>
+      </c>
+      <c r="F52" s="65">
+        <v>99038.604734399996</v>
+      </c>
+      <c r="G52" s="76" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.6">
+      <c r="A53" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" s="40">
+        <v>176487.6179442</v>
+      </c>
+      <c r="C53" s="40">
+        <v>177813.59379595</v>
+      </c>
+      <c r="D53" s="66">
+        <v>7.5131101522882826E-3</v>
+      </c>
+      <c r="E53" s="40">
+        <v>1955995.4781600998</v>
+      </c>
+      <c r="F53" s="40">
+        <v>2033804.6731173501</v>
+      </c>
+      <c r="G53" s="66">
+        <v>3.977984398534562E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="B54" s="22"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.45" right="0.45" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="70" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93C3BEF-E8A4-4138-BA47-42E8AAF626CE}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="38.44140625" customWidth="1"/>
+    <col min="2" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="6" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="16.05" customHeight="1">
+      <c r="A1" s="167" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.6">
+      <c r="A2" s="108"/>
+      <c r="B2" s="170" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.6">
+      <c r="A3" s="109" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="111">
+        <v>46113</v>
+      </c>
+      <c r="D3" s="109" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="111">
+        <v>46113</v>
+      </c>
+      <c r="G3" s="109" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6">
+      <c r="A4" s="109" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="111" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="109" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="109" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="109" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" collapsed="1">
+      <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="I5" s="22"/>
+    </row>
+    <row r="6" spans="1:11" outlineLevel="1">
+      <c r="A6" s="127" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="150">
+        <v>48633.708700000003</v>
+      </c>
+      <c r="C6" s="150">
+        <v>52140.25</v>
+      </c>
+      <c r="D6" s="150"/>
+      <c r="E6" s="150">
+        <v>48633.708700000003</v>
+      </c>
+      <c r="F6" s="150">
+        <v>52140.25</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="128"/>
+    </row>
+    <row r="7" spans="1:11" outlineLevel="1">
+      <c r="A7" s="127" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="150">
+        <v>59372.423699999999</v>
+      </c>
+      <c r="C7" s="150">
+        <v>61330.58</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="150">
+        <v>59372.423699999999</v>
+      </c>
+      <c r="F7" s="150">
+        <v>61330.58</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="I7" s="128"/>
+    </row>
+    <row r="8" spans="1:11" outlineLevel="1">
+      <c r="A8" s="127" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="150">
+        <v>69504.392699999997</v>
+      </c>
+      <c r="C8" s="150">
+        <v>71651.240000000005</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="150">
+        <v>69504.392699999997</v>
+      </c>
+      <c r="F8" s="150">
+        <v>71651.240000000005</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="138"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="136" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="6">
+        <v>177510.5251</v>
+      </c>
+      <c r="C9" s="6">
+        <v>185122.07</v>
+      </c>
+      <c r="D9" s="9">
+        <v>4.2879400507164656E-2</v>
+      </c>
+      <c r="E9" s="8">
+        <v>177510.5251</v>
+      </c>
+      <c r="F9" s="8">
+        <v>185122.07</v>
+      </c>
+      <c r="G9" s="9">
+        <v>4.2879400507164656E-2</v>
+      </c>
+      <c r="I9" s="22"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="14"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="9"/>
+      <c r="I10" s="22"/>
+    </row>
+    <row r="11" spans="1:11" ht="12.75" customHeight="1" collapsed="1">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="9"/>
+      <c r="I11" s="22"/>
+    </row>
+    <row r="12" spans="1:11" outlineLevel="1">
+      <c r="A12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="162">
+        <v>45754.49</v>
+      </c>
+      <c r="C12" s="162">
+        <v>57580.406101599998</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11">
+        <v>45754.49</v>
+      </c>
+      <c r="F12" s="11">
+        <v>57580.406101599998</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="I12" s="22"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="6">
+        <v>45754.49</v>
+      </c>
+      <c r="C13" s="6">
+        <v>57580.406101599998</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0.25846460318102116</v>
+      </c>
+      <c r="E13" s="151">
+        <v>45754.49</v>
+      </c>
+      <c r="F13" s="6">
+        <v>57580.406101599998</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0.25846460318102116</v>
+      </c>
+      <c r="I13" s="48"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="9"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="113"/>
+      <c r="K14" s="22"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.6">
+      <c r="A15" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="57">
+        <v>48633.708700000003</v>
+      </c>
+      <c r="C15" s="57">
+        <v>52140.25</v>
+      </c>
+      <c r="D15" s="52"/>
+      <c r="E15" s="57">
+        <v>48633.708700000003</v>
+      </c>
+      <c r="F15" s="57">
+        <v>52140.25</v>
+      </c>
+      <c r="G15" s="52"/>
+      <c r="I15" s="22"/>
+    </row>
+    <row r="16" spans="1:11" ht="15.6">
+      <c r="A16" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="57">
+        <v>59372.423699999999</v>
+      </c>
+      <c r="C16" s="57">
+        <v>61330.58</v>
+      </c>
+      <c r="D16" s="52"/>
+      <c r="E16" s="57">
+        <v>59372.423699999999</v>
+      </c>
+      <c r="F16" s="57">
+        <v>61330.58</v>
+      </c>
+      <c r="G16" s="52"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.6">
+      <c r="A17" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="57">
+        <v>115258.88269999999</v>
+      </c>
+      <c r="C17" s="57">
+        <v>129231.6461016</v>
+      </c>
+      <c r="D17" s="52"/>
+      <c r="E17" s="57">
+        <v>115258.88269999999</v>
+      </c>
+      <c r="F17" s="57">
+        <v>129231.6461016</v>
+      </c>
+      <c r="G17" s="52"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.6">
+      <c r="A18" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="87">
+        <v>223265.01509999999</v>
+      </c>
+      <c r="C18" s="87">
+        <v>242702.47610159998</v>
+      </c>
+      <c r="D18" s="19">
+        <v>8.7060039356788632E-2</v>
+      </c>
+      <c r="E18" s="87">
+        <v>223265.01509999999</v>
+      </c>
+      <c r="F18" s="87">
+        <v>242702.47610159998</v>
+      </c>
+      <c r="G18" s="19">
+        <v>8.7060039356788632E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="20" customFormat="1" collapsed="1">
+      <c r="A19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="114"/>
+      <c r="E19" s="94"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="84"/>
+    </row>
+    <row r="20" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="68">
+        <v>3230.81</v>
+      </c>
+      <c r="C20" s="68">
+        <v>5253.16</v>
+      </c>
+      <c r="D20" s="11"/>
+      <c r="E20" s="94">
+        <v>3230.81</v>
+      </c>
+      <c r="F20" s="94">
+        <v>5253.16</v>
+      </c>
+      <c r="G20" s="12"/>
+    </row>
+    <row r="21" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A21" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="68">
+        <v>3845.73</v>
+      </c>
+      <c r="C21" s="68">
+        <v>5889.02</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="94">
+        <v>3845.73</v>
+      </c>
+      <c r="F21" s="94">
+        <v>5889.02</v>
+      </c>
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="68">
+        <v>5854.17</v>
+      </c>
+      <c r="C22" s="68">
+        <v>8854.119999999999</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="94">
+        <v>5854.17</v>
+      </c>
+      <c r="F22" s="94">
+        <v>8854.119999999999</v>
+      </c>
+      <c r="G22" s="12"/>
+    </row>
+    <row r="23" spans="1:10" s="20" customFormat="1">
+      <c r="A23" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="6">
+        <v>12930.71</v>
+      </c>
+      <c r="C23" s="6">
+        <v>19996.3</v>
+      </c>
+      <c r="D23" s="23">
+        <v>0.54641933814925858</v>
+      </c>
+      <c r="E23" s="6">
+        <v>12930.71</v>
+      </c>
+      <c r="F23" s="6">
+        <v>19996.3</v>
+      </c>
+      <c r="G23" s="23">
+        <v>0.54641933814925858</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="20" customFormat="1" collapsed="1">
+      <c r="A24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="153"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="62"/>
+    </row>
+    <row r="25" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="150">
+        <v>13716.32</v>
+      </c>
+      <c r="C25" s="150">
+        <v>11796.694172899999</v>
+      </c>
+      <c r="D25" s="150"/>
+      <c r="E25" s="150">
+        <v>13716.32</v>
+      </c>
+      <c r="F25" s="150">
+        <v>11796.694172899999</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="21"/>
+    </row>
+    <row r="26" spans="1:10" s="20" customFormat="1">
+      <c r="A26" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="6">
+        <v>13716.32</v>
+      </c>
+      <c r="C26" s="6">
+        <v>11796.694172899999</v>
+      </c>
+      <c r="D26" s="23">
+        <v>-0.13995195701908392</v>
+      </c>
+      <c r="E26" s="6">
+        <v>13716.32</v>
+      </c>
+      <c r="F26" s="6">
+        <v>11796.694172899999</v>
+      </c>
+      <c r="G26" s="23">
+        <v>-0.13995195701908392</v>
+      </c>
+      <c r="H26" s="21"/>
+      <c r="I26"/>
+      <c r="J26" s="81"/>
+    </row>
+    <row r="27" spans="1:10" s="20" customFormat="1">
+      <c r="A27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="21"/>
+      <c r="I27"/>
+    </row>
+    <row r="28" spans="1:10" s="20" customFormat="1">
+      <c r="A28" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="28">
+        <v>3230.81</v>
+      </c>
+      <c r="C28" s="28">
+        <v>5253.16</v>
+      </c>
+      <c r="D28" s="29"/>
+      <c r="E28" s="28">
+        <v>3230.81</v>
+      </c>
+      <c r="F28" s="28">
+        <v>5253.16</v>
+      </c>
+      <c r="G28" s="24"/>
+      <c r="H28" s="21"/>
+      <c r="I28"/>
+    </row>
+    <row r="29" spans="1:10" s="20" customFormat="1">
+      <c r="A29" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="28">
+        <v>3845.73</v>
+      </c>
+      <c r="C29" s="28">
+        <v>5889.02</v>
+      </c>
+      <c r="D29" s="29"/>
+      <c r="E29" s="28">
+        <v>3845.73</v>
+      </c>
+      <c r="F29" s="28">
+        <v>5889.02</v>
+      </c>
+      <c r="G29" s="24"/>
+      <c r="H29" s="21"/>
+      <c r="I29"/>
+    </row>
+    <row r="30" spans="1:10" s="20" customFormat="1">
+      <c r="A30" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="28">
+        <v>19570.489999999998</v>
+      </c>
+      <c r="C30" s="28">
+        <v>20650.814172899998</v>
+      </c>
+      <c r="D30" s="29"/>
+      <c r="E30" s="28">
+        <v>19570.489999999998</v>
+      </c>
+      <c r="F30" s="28">
+        <v>20650.814172899998</v>
+      </c>
+      <c r="G30" s="24"/>
+      <c r="H30" s="21"/>
+      <c r="I30"/>
+    </row>
+    <row r="31" spans="1:10" s="20" customFormat="1" ht="15.6">
+      <c r="A31" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="96">
+        <v>26647.03</v>
+      </c>
+      <c r="C31" s="96">
+        <v>31792.994172899998</v>
+      </c>
+      <c r="D31" s="31">
+        <v>0.19311586217676036</v>
+      </c>
+      <c r="E31" s="96">
+        <v>26647.03</v>
+      </c>
+      <c r="F31" s="96">
+        <v>31792.994172899998</v>
+      </c>
+      <c r="G31" s="31">
+        <v>0.19311586217676036</v>
+      </c>
+      <c r="H31" s="21"/>
+      <c r="I31"/>
+    </row>
+    <row r="32" spans="1:10" s="20" customFormat="1">
+      <c r="A32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="21"/>
+      <c r="I32"/>
+    </row>
+    <row r="33" spans="1:9" s="20" customFormat="1">
+      <c r="A33" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="28">
+        <v>45402.898700000005</v>
+      </c>
+      <c r="C33" s="28">
+        <v>46887.09</v>
+      </c>
+      <c r="D33" s="28">
+        <v>0</v>
+      </c>
+      <c r="E33" s="28">
+        <v>45402.898700000005</v>
+      </c>
+      <c r="F33" s="28">
+        <v>46887.09</v>
+      </c>
+      <c r="G33" s="29"/>
+      <c r="H33" s="21"/>
+      <c r="I33"/>
+    </row>
+    <row r="34" spans="1:9" s="20" customFormat="1">
+      <c r="A34" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="28">
+        <v>55526.693699999996</v>
+      </c>
+      <c r="C34" s="28">
+        <v>55441.56</v>
+      </c>
+      <c r="D34" s="28">
+        <v>0</v>
+      </c>
+      <c r="E34" s="28">
+        <v>55526.693699999996</v>
+      </c>
+      <c r="F34" s="28">
+        <v>55441.56</v>
+      </c>
+      <c r="G34" s="29"/>
+      <c r="H34" s="21"/>
+      <c r="I34"/>
+    </row>
+    <row r="35" spans="1:9" s="20" customFormat="1">
+      <c r="A35" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="28">
+        <v>63650.222699999998</v>
+      </c>
+      <c r="C35" s="28">
+        <v>62797.12000000001</v>
+      </c>
+      <c r="D35" s="28">
+        <v>0</v>
+      </c>
+      <c r="E35" s="28">
+        <v>63650.222699999998</v>
+      </c>
+      <c r="F35" s="28">
+        <v>62797.12000000001</v>
+      </c>
+      <c r="G35" s="29"/>
+      <c r="H35" s="21"/>
+      <c r="I35"/>
+    </row>
+    <row r="36" spans="1:9" s="20" customFormat="1">
+      <c r="A36" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="88">
+        <v>164579.81510000001</v>
+      </c>
+      <c r="C36" s="88">
+        <v>165125.77000000002</v>
+      </c>
+      <c r="D36" s="23">
+        <v>3.3172652409914072E-3</v>
+      </c>
+      <c r="E36" s="88">
+        <v>164579.81510000001</v>
+      </c>
+      <c r="F36" s="88">
+        <v>165125.77000000002</v>
+      </c>
+      <c r="G36" s="23">
+        <v>3.3172652409914072E-3</v>
+      </c>
+      <c r="H36" s="21"/>
+      <c r="I36"/>
+    </row>
+    <row r="37" spans="1:9" s="20" customFormat="1">
+      <c r="A37" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="21"/>
+      <c r="I37"/>
+    </row>
+    <row r="38" spans="1:9" s="20" customFormat="1">
+      <c r="A38" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="28">
+        <v>32038.17</v>
+      </c>
+      <c r="C38" s="28">
+        <v>45783.711928699995</v>
+      </c>
+      <c r="D38" s="28">
+        <v>0</v>
+      </c>
+      <c r="E38" s="28">
+        <v>32038.17</v>
+      </c>
+      <c r="F38" s="28">
+        <v>45783.711928699995</v>
+      </c>
+      <c r="G38" s="29"/>
+      <c r="H38" s="21"/>
+      <c r="I38"/>
+    </row>
+    <row r="39" spans="1:9" s="20" customFormat="1">
+      <c r="A39" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="88">
+        <v>32038.17</v>
+      </c>
+      <c r="C39" s="88">
+        <v>45783.711928699995</v>
+      </c>
+      <c r="D39" s="23">
+        <v>0.42903642526086849</v>
+      </c>
+      <c r="E39" s="88">
+        <v>32038.17</v>
+      </c>
+      <c r="F39" s="88">
+        <v>45783.711928699995</v>
+      </c>
+      <c r="G39" s="23">
+        <v>0.42903642526086849</v>
+      </c>
+      <c r="H39" s="21"/>
+      <c r="I39"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="9"/>
+    </row>
+    <row r="41" spans="1:9" ht="15.6">
+      <c r="A41" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="57">
+        <v>45402.898700000005</v>
+      </c>
+      <c r="C41" s="57">
+        <v>46887.09</v>
+      </c>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57">
+        <v>45402.898700000005</v>
+      </c>
+      <c r="F41" s="57">
+        <v>46887.09</v>
+      </c>
+      <c r="G41" s="52"/>
+    </row>
+    <row r="42" spans="1:9" ht="15.6">
+      <c r="A42" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="57">
+        <v>55526.693699999996</v>
+      </c>
+      <c r="C42" s="57">
+        <v>55441.56</v>
+      </c>
+      <c r="D42" s="52"/>
+      <c r="E42" s="57">
+        <v>55526.693699999996</v>
+      </c>
+      <c r="F42" s="57">
+        <v>55441.56</v>
+      </c>
+      <c r="G42" s="52"/>
+    </row>
+    <row r="43" spans="1:9" ht="15.6">
+      <c r="A43" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="89">
+        <v>95688.392699999997</v>
+      </c>
+      <c r="C43" s="89">
+        <v>108580.8319287</v>
+      </c>
+      <c r="D43" s="52"/>
+      <c r="E43" s="89">
+        <v>95688.392699999997</v>
+      </c>
+      <c r="F43" s="89">
+        <v>108580.8319287</v>
+      </c>
+      <c r="G43" s="52"/>
+    </row>
+    <row r="44" spans="1:9" ht="15.6">
+      <c r="A44" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" s="87">
+        <v>196617.98509999999</v>
+      </c>
+      <c r="C44" s="87">
+        <v>210909.4819287</v>
+      </c>
+      <c r="D44" s="19">
+        <v>7.26866203080625E-2</v>
+      </c>
+      <c r="E44" s="87">
+        <v>196617.98509999999</v>
+      </c>
+      <c r="F44" s="87">
+        <v>210909.4819287</v>
+      </c>
+      <c r="G44" s="19">
+        <v>7.26866203080625E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="74"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="74"/>
+    </row>
+    <row r="47" spans="1:9" ht="15.6">
+      <c r="A47" s="163" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="15.6">
+      <c r="A48" s="164" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="91">
+        <v>12292.883300000001</v>
+      </c>
+      <c r="C48" s="91">
+        <v>67.69</v>
+      </c>
+      <c r="D48" s="91"/>
+      <c r="E48" s="91">
+        <v>12292.883300000001</v>
+      </c>
+      <c r="F48" s="91">
+        <v>67.69</v>
+      </c>
+      <c r="G48" s="91"/>
+    </row>
+    <row r="49" spans="1:7" ht="15.6">
+      <c r="A49" s="164" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" s="91">
+        <v>1158.58</v>
+      </c>
+      <c r="C49" s="91">
+        <v>2.00001E-2</v>
+      </c>
+      <c r="D49" s="91"/>
+      <c r="E49" s="91">
+        <v>1158.58</v>
+      </c>
+      <c r="F49" s="91">
+        <v>2.00001E-2</v>
+      </c>
+      <c r="G49" s="91"/>
+    </row>
+    <row r="50" spans="1:7" ht="15.6">
+      <c r="A50" s="164" t="s">
+        <v>132</v>
+      </c>
+      <c r="B50" s="91">
+        <v>-689.57178629999999</v>
+      </c>
+      <c r="C50" s="91">
+        <v>-203.41474909999999</v>
+      </c>
+      <c r="D50" s="91"/>
+      <c r="E50" s="91">
+        <v>-689.57178629999999</v>
+      </c>
+      <c r="F50" s="91">
+        <v>-203.41474909999999</v>
+      </c>
+      <c r="G50" s="91"/>
+    </row>
+    <row r="51" spans="1:7" ht="15.6">
+      <c r="A51" s="165" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" s="96">
+        <v>12761.8915137</v>
+      </c>
+      <c r="C51" s="96">
+        <v>-135.70474899999999</v>
+      </c>
+      <c r="D51" s="96"/>
+      <c r="E51" s="96">
+        <v>12761.8915137</v>
+      </c>
+      <c r="F51" s="96">
+        <v>-135.70474899999999</v>
+      </c>
+      <c r="G51" s="96"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.45" right="0.45" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="67" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF74A71-B96C-484E-AEBF-069B054D0BD4}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="38.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="6" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6">
+      <c r="A1" s="167" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.6">
+      <c r="A2" s="108"/>
+      <c r="B2" s="170" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="171" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="168"/>
+      <c r="G2" s="169"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.6">
+      <c r="A3" s="109" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="110" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="111">
+        <v>46143</v>
+      </c>
+      <c r="D3" s="109" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="110" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" s="111">
+        <v>46143</v>
+      </c>
+      <c r="G3" s="109" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6">
+      <c r="A4" s="109" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="111" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="109" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="110" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="111" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="109" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" collapsed="1">
+      <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="I5" s="22"/>
+    </row>
+    <row r="6" spans="1:11" outlineLevel="1">
+      <c r="A6" s="127" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="77">
+        <v>35433.745000000003</v>
+      </c>
+      <c r="C6" s="77">
+        <v>37397.040000000001</v>
+      </c>
+      <c r="D6" s="107"/>
+      <c r="E6" s="77">
+        <v>84067.45</v>
+      </c>
+      <c r="F6" s="77">
+        <v>89537.279999999999</v>
+      </c>
+      <c r="G6" s="80"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="128"/>
+    </row>
+    <row r="7" spans="1:11" outlineLevel="1">
+      <c r="A7" s="127" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="77">
+        <v>43901.584900000002</v>
+      </c>
+      <c r="C7" s="77">
+        <v>45143.22</v>
+      </c>
+      <c r="D7" s="104"/>
+      <c r="E7" s="77">
+        <v>103274.01</v>
+      </c>
+      <c r="F7" s="77">
+        <v>106473.8</v>
+      </c>
+      <c r="G7" s="80"/>
+      <c r="I7" s="128"/>
+    </row>
+    <row r="8" spans="1:11" outlineLevel="1">
+      <c r="A8" s="127" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="77">
+        <v>58766.680500000002</v>
+      </c>
+      <c r="C8" s="77">
+        <v>51990.19</v>
+      </c>
+      <c r="D8" s="104"/>
+      <c r="E8" s="77">
+        <v>128271.07</v>
+      </c>
+      <c r="F8" s="77">
+        <v>123641.43</v>
+      </c>
+      <c r="G8" s="80"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="138"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="136" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="118">
+        <v>138102.01040000003</v>
+      </c>
+      <c r="C9" s="35">
+        <v>134530.45000000001</v>
+      </c>
+      <c r="D9" s="61">
+        <v>-2.5861752482820521E-2</v>
+      </c>
+      <c r="E9" s="73">
+        <v>315612.53000000003</v>
+      </c>
+      <c r="F9" s="73">
+        <v>319652.51</v>
+      </c>
+      <c r="G9" s="61">
+        <v>1.2800442365200171E-2</v>
+      </c>
+      <c r="I9" s="22"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="14"/>
+      <c r="B10" s="118"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="61"/>
+      <c r="I10" s="22"/>
+    </row>
+    <row r="11" spans="1:11" ht="12.75" customHeight="1" collapsed="1">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="61"/>
+      <c r="I11" s="22"/>
+    </row>
+    <row r="12" spans="1:11" outlineLevel="1">
+      <c r="A12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="141">
+        <v>50069.71</v>
+      </c>
+      <c r="C12" s="141">
+        <v>59653.8985875</v>
+      </c>
+      <c r="D12" s="104"/>
+      <c r="E12" s="34">
+        <v>95824.2</v>
+      </c>
+      <c r="F12" s="34">
+        <v>117234.30858750001</v>
+      </c>
+      <c r="G12" s="80"/>
+      <c r="I12" s="22"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="35">
+        <v>50069.71</v>
+      </c>
+      <c r="C13" s="35">
+        <v>59653.8985875</v>
+      </c>
+      <c r="D13" s="61">
+        <v>0.19141689831037567</v>
+      </c>
+      <c r="E13" s="35">
+        <v>95824.2</v>
+      </c>
+      <c r="F13" s="35">
+        <v>117234.30858750001</v>
+      </c>
+      <c r="G13" s="63">
+        <v>0.22343112269656329</v>
+      </c>
+      <c r="I13" s="48"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="61"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="113"/>
+      <c r="K14" s="22"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.6">
+      <c r="A15" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="75">
+        <v>35433.745000000003</v>
+      </c>
+      <c r="C15" s="65">
+        <v>37397.040000000001</v>
+      </c>
+      <c r="D15" s="76"/>
+      <c r="E15" s="65">
+        <v>84067.45</v>
+      </c>
+      <c r="F15" s="65">
+        <v>89537.279999999999</v>
+      </c>
+      <c r="G15" s="76"/>
+      <c r="I15" s="22"/>
+    </row>
+    <row r="16" spans="1:11" ht="15.6">
+      <c r="A16" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="75">
+        <v>43901.584900000002</v>
+      </c>
+      <c r="C16" s="65">
+        <v>45143.22</v>
+      </c>
+      <c r="D16" s="76"/>
+      <c r="E16" s="65">
+        <v>103274.01</v>
+      </c>
+      <c r="F16" s="65">
+        <v>106473.8</v>
+      </c>
+      <c r="G16" s="76"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.6">
+      <c r="A17" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="75">
+        <v>108836.39050000001</v>
+      </c>
+      <c r="C17" s="65">
+        <v>111644.08858750001</v>
+      </c>
+      <c r="D17" s="76"/>
+      <c r="E17" s="65">
+        <v>224095.27000000002</v>
+      </c>
+      <c r="F17" s="65">
+        <v>240875.7385875</v>
+      </c>
+      <c r="G17" s="76"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.6">
+      <c r="A18" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="40">
+        <v>188171.72040000002</v>
+      </c>
+      <c r="C18" s="40">
+        <v>194184.34858750002</v>
+      </c>
+      <c r="D18" s="66">
+        <v>3.1952881057260019E-2</v>
+      </c>
+      <c r="E18" s="40">
+        <v>411436.73</v>
+      </c>
+      <c r="F18" s="40">
+        <v>436886.81858750002</v>
+      </c>
+      <c r="G18" s="66">
+        <v>6.1856627597395297E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="20" customFormat="1" collapsed="1">
+      <c r="A19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="104"/>
+    </row>
+    <row r="20" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="77">
+        <v>4223.59</v>
+      </c>
+      <c r="C20" s="77">
+        <v>4117.6000000000004</v>
+      </c>
+      <c r="D20" s="104"/>
+      <c r="E20" s="59">
+        <v>7454.4</v>
+      </c>
+      <c r="F20" s="59">
+        <v>9366.65</v>
+      </c>
+      <c r="G20" s="80"/>
+    </row>
+    <row r="21" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A21" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="77">
+        <v>5371.39</v>
+      </c>
+      <c r="C21" s="77">
+        <v>5471.72</v>
+      </c>
+      <c r="D21" s="104"/>
+      <c r="E21" s="59">
+        <v>9217.11</v>
+      </c>
+      <c r="F21" s="59">
+        <v>11355.82</v>
+      </c>
+      <c r="G21" s="80"/>
+    </row>
+    <row r="22" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="77">
+        <v>8198.17</v>
+      </c>
+      <c r="C22" s="77">
+        <v>7440.76</v>
+      </c>
+      <c r="D22" s="104"/>
+      <c r="E22" s="59">
+        <v>14052.33</v>
+      </c>
+      <c r="F22" s="59">
+        <v>16292.93</v>
+      </c>
+      <c r="G22" s="80"/>
+    </row>
+    <row r="23" spans="1:10" s="20" customFormat="1">
+      <c r="A23" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="78">
+        <v>17793.150000000001</v>
+      </c>
+      <c r="C23" s="35">
+        <v>17030.080000000002</v>
+      </c>
+      <c r="D23" s="63">
+        <v>-4.2885604853553194E-2</v>
+      </c>
+      <c r="E23" s="35">
+        <v>30723.840000000004</v>
+      </c>
+      <c r="F23" s="35">
+        <v>37015.4</v>
+      </c>
+      <c r="G23" s="63">
+        <v>0.20477778819314252</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="20" customFormat="1" collapsed="1">
+      <c r="A24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="104"/>
+    </row>
+    <row r="25" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="77">
+        <v>8793.5499999999993</v>
+      </c>
+      <c r="C25" s="77">
+        <v>10250.482122900001</v>
+      </c>
+      <c r="D25" s="107"/>
+      <c r="E25" s="77">
+        <v>22509.872205799998</v>
+      </c>
+      <c r="F25" s="77">
+        <v>22047.182122900002</v>
+      </c>
+      <c r="G25" s="80"/>
+      <c r="H25" s="21"/>
+    </row>
+    <row r="26" spans="1:10" s="20" customFormat="1">
+      <c r="A26" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="35">
+        <v>8793.5499999999993</v>
+      </c>
+      <c r="C26" s="35">
+        <v>10250.482122900001</v>
+      </c>
+      <c r="D26" s="63">
+        <v>0.16568161341432042</v>
+      </c>
+      <c r="E26" s="35">
+        <v>22509.872205799998</v>
+      </c>
+      <c r="F26" s="35">
+        <v>22047.182122900002</v>
+      </c>
+      <c r="G26" s="63">
+        <v>-2.0554984882623084E-2</v>
+      </c>
+      <c r="H26" s="21"/>
+      <c r="I26"/>
+      <c r="J26" s="81"/>
+    </row>
+    <row r="27" spans="1:10" s="20" customFormat="1">
+      <c r="A27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="21"/>
+      <c r="I27"/>
+    </row>
+    <row r="28" spans="1:10" s="20" customFormat="1">
+      <c r="A28" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="42">
+        <v>4223.59</v>
+      </c>
+      <c r="C28" s="42">
+        <v>4117.6000000000004</v>
+      </c>
+      <c r="D28" s="82"/>
+      <c r="E28" s="42">
+        <v>7454.4</v>
+      </c>
+      <c r="F28" s="42">
+        <v>9366.65</v>
+      </c>
+      <c r="G28" s="63"/>
+      <c r="H28" s="21"/>
+      <c r="I28"/>
+    </row>
+    <row r="29" spans="1:10" s="20" customFormat="1">
+      <c r="A29" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="42">
+        <v>5371.39</v>
+      </c>
+      <c r="C29" s="42">
+        <v>5471.72</v>
+      </c>
+      <c r="D29" s="82"/>
+      <c r="E29" s="42">
+        <v>9217.11</v>
+      </c>
+      <c r="F29" s="42">
+        <v>11355.82</v>
+      </c>
+      <c r="G29" s="63"/>
+      <c r="H29" s="21"/>
+      <c r="I29"/>
+    </row>
+    <row r="30" spans="1:10" s="20" customFormat="1">
+      <c r="A30" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="42">
+        <v>16991.72</v>
+      </c>
+      <c r="C30" s="42">
+        <v>17691.242122900003</v>
+      </c>
+      <c r="D30" s="82"/>
+      <c r="E30" s="42">
+        <v>36562.2022058</v>
+      </c>
+      <c r="F30" s="42">
+        <v>38340.112122899998</v>
+      </c>
+      <c r="G30" s="63"/>
+      <c r="H30" s="21"/>
+      <c r="I30"/>
+    </row>
+    <row r="31" spans="1:10" s="20" customFormat="1" ht="15.6">
+      <c r="A31" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="40">
+        <v>26586.7</v>
+      </c>
+      <c r="C31" s="40">
+        <v>27280.562122900003</v>
+      </c>
+      <c r="D31" s="66">
+        <v>2.6098006128365769E-2</v>
+      </c>
+      <c r="E31" s="40">
+        <v>53233.712205800002</v>
+      </c>
+      <c r="F31" s="40">
+        <v>59062.582122899999</v>
+      </c>
+      <c r="G31" s="66">
+        <v>0.10949583779853178</v>
+      </c>
+      <c r="H31" s="21"/>
+      <c r="I31"/>
+    </row>
+    <row r="32" spans="1:10" s="20" customFormat="1">
+      <c r="A32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="21"/>
+      <c r="I32"/>
+    </row>
+    <row r="33" spans="1:9" s="20" customFormat="1">
+      <c r="A33" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="42">
+        <v>31210.155000000002</v>
+      </c>
+      <c r="C33" s="42">
+        <v>33279.440000000002</v>
+      </c>
+      <c r="D33" s="82">
+        <v>0</v>
+      </c>
+      <c r="E33" s="42">
+        <v>76613.05</v>
+      </c>
+      <c r="F33" s="42">
+        <v>80170.63</v>
+      </c>
+      <c r="G33" s="82"/>
+      <c r="H33" s="21"/>
+      <c r="I33"/>
+    </row>
+    <row r="34" spans="1:9" s="20" customFormat="1">
+      <c r="A34" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="42">
+        <v>38530.194900000002</v>
+      </c>
+      <c r="C34" s="42">
+        <v>39671.5</v>
+      </c>
+      <c r="D34" s="82">
+        <v>0</v>
+      </c>
+      <c r="E34" s="42">
+        <v>94056.9</v>
+      </c>
+      <c r="F34" s="42">
+        <v>95117.98000000001</v>
+      </c>
+      <c r="G34" s="82"/>
+      <c r="H34" s="21"/>
+      <c r="I34"/>
+    </row>
+    <row r="35" spans="1:9" s="20" customFormat="1">
+      <c r="A35" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="42">
+        <v>50568.510500000004</v>
+      </c>
+      <c r="C35" s="42">
+        <v>44549.43</v>
+      </c>
+      <c r="D35" s="82">
+        <v>0</v>
+      </c>
+      <c r="E35" s="42">
+        <v>114218.74</v>
+      </c>
+      <c r="F35" s="42">
+        <v>107348.5</v>
+      </c>
+      <c r="G35" s="82"/>
+      <c r="H35" s="21"/>
+      <c r="I35"/>
+    </row>
+    <row r="36" spans="1:9" s="20" customFormat="1">
+      <c r="A36" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="43">
+        <v>120308.86040000001</v>
+      </c>
+      <c r="C36" s="43">
+        <v>117500.37</v>
+      </c>
+      <c r="D36" s="63">
+        <v>-2.3343999768595802E-2</v>
+      </c>
+      <c r="E36" s="43">
+        <v>284888.69</v>
+      </c>
+      <c r="F36" s="43">
+        <v>282637.11</v>
+      </c>
+      <c r="G36" s="63">
+        <v>-7.9033674520390118E-3</v>
+      </c>
+      <c r="H36" s="21"/>
+      <c r="I36"/>
+    </row>
+    <row r="37" spans="1:9" s="20" customFormat="1">
+      <c r="A37" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="35"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="21"/>
+      <c r="I37"/>
+    </row>
+    <row r="38" spans="1:9" s="20" customFormat="1">
+      <c r="A38" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="42">
+        <v>41276.160000000003</v>
+      </c>
+      <c r="C38" s="42">
+        <v>49403.416464599999</v>
+      </c>
+      <c r="D38" s="82">
+        <v>0</v>
+      </c>
+      <c r="E38" s="42">
+        <v>73314.327794199999</v>
+      </c>
+      <c r="F38" s="42">
+        <v>95187.126464600005</v>
+      </c>
+      <c r="G38" s="82"/>
+      <c r="H38" s="21"/>
+      <c r="I38"/>
+    </row>
+    <row r="39" spans="1:9" s="20" customFormat="1">
+      <c r="A39" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="43">
+        <v>41276.160000000003</v>
+      </c>
+      <c r="C39" s="43">
+        <v>49403.416464599999</v>
+      </c>
+      <c r="D39" s="63">
+        <v>0.19689959300286453</v>
+      </c>
+      <c r="E39" s="43">
+        <v>73314.327794199999</v>
+      </c>
+      <c r="F39" s="43">
+        <v>95187.126464600005</v>
+      </c>
+      <c r="G39" s="63">
+        <v>0.29834275684555056</v>
+      </c>
+      <c r="H39" s="21"/>
+      <c r="I39"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="61"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="61"/>
+    </row>
+    <row r="41" spans="1:9" ht="15.6">
+      <c r="A41" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="65">
+        <v>31210.155000000002</v>
+      </c>
+      <c r="C41" s="65">
+        <v>33279.440000000002</v>
+      </c>
+      <c r="D41" s="76"/>
+      <c r="E41" s="65">
+        <v>76613.05</v>
+      </c>
+      <c r="F41" s="65">
+        <v>80170.63</v>
+      </c>
+      <c r="G41" s="76"/>
+    </row>
+    <row r="42" spans="1:9" ht="15.6">
+      <c r="A42" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="65">
+        <v>38530.194900000002</v>
+      </c>
+      <c r="C42" s="65">
+        <v>39671.5</v>
+      </c>
+      <c r="D42" s="76"/>
+      <c r="E42" s="65">
+        <v>94056.9</v>
+      </c>
+      <c r="F42" s="65">
+        <v>95117.98000000001</v>
+      </c>
+      <c r="G42" s="76"/>
+    </row>
+    <row r="43" spans="1:9" ht="15.6">
+      <c r="A43" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="65">
+        <v>91844.670500000007</v>
+      </c>
+      <c r="C43" s="65">
+        <v>93952.846464600007</v>
+      </c>
+      <c r="D43" s="76"/>
+      <c r="E43" s="65">
+        <v>187533.0677942</v>
+      </c>
+      <c r="F43" s="65">
+        <v>202535.62646460001</v>
+      </c>
+      <c r="G43" s="76"/>
+    </row>
+    <row r="44" spans="1:9" ht="15.6">
+      <c r="A44" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" s="40">
+        <v>161585.02040000001</v>
+      </c>
+      <c r="C44" s="40">
+        <v>166903.78646460001</v>
+      </c>
+      <c r="D44" s="66">
+        <v>3.2916224183445975E-2</v>
+      </c>
+      <c r="E44" s="40">
+        <v>358203.01779419999</v>
+      </c>
+      <c r="F44" s="40">
+        <v>377824.23646460002</v>
+      </c>
+      <c r="G44" s="66">
+        <v>5.4776810064936621E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="B45" s="58"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="166"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="166"/>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="B46" s="58"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="166"/>
+      <c r="E46" s="58"/>
+      <c r="F46" s="58"/>
+      <c r="G46" s="166"/>
+    </row>
+    <row r="47" spans="1:9" ht="15.6">
+      <c r="A47" s="163" t="s">
+        <v>129</v>
+      </c>
+      <c r="B47" s="58"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="166"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="166"/>
+    </row>
+    <row r="48" spans="1:9" ht="15.6">
+      <c r="A48" s="164" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="34">
+        <v>11682.6384</v>
+      </c>
+      <c r="C48" s="34">
+        <v>43.61</v>
+      </c>
+      <c r="D48" s="104"/>
+      <c r="E48" s="34">
+        <v>23975.52</v>
+      </c>
+      <c r="F48" s="34">
+        <v>111.3</v>
+      </c>
+      <c r="G48" s="104"/>
+    </row>
+    <row r="49" spans="1:7" ht="15.6">
+      <c r="A49" s="164" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" s="34">
+        <v>1196</v>
+      </c>
+      <c r="C49" s="34">
+        <v>6.2374699999999998E-2</v>
+      </c>
+      <c r="D49" s="104"/>
+      <c r="E49" s="34">
+        <v>2354.58</v>
+      </c>
+      <c r="F49" s="34">
+        <v>8.2374699999999995E-2</v>
+      </c>
+      <c r="G49" s="104"/>
+    </row>
+    <row r="50" spans="1:7" ht="15.6">
+      <c r="A50" s="164" t="s">
+        <v>132</v>
+      </c>
+      <c r="B50" s="34">
+        <v>-416.59999999999997</v>
+      </c>
+      <c r="C50" s="34">
+        <v>-161.80955370000001</v>
+      </c>
+      <c r="D50" s="104"/>
+      <c r="E50" s="34">
+        <v>-1106.1693485000001</v>
+      </c>
+      <c r="F50" s="34">
+        <v>-365.19955369999997</v>
+      </c>
+      <c r="G50" s="104"/>
+    </row>
+    <row r="51" spans="1:7" ht="15.6">
+      <c r="A51" s="165" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" s="40">
+        <v>12462.038399999999</v>
+      </c>
+      <c r="C51" s="40">
+        <v>-118.137179</v>
+      </c>
+      <c r="D51" s="66"/>
+      <c r="E51" s="40">
+        <v>25223.930651499999</v>
+      </c>
+      <c r="F51" s="40">
+        <v>-253.81717899999995</v>
+      </c>
+      <c r="G51" s="66"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.45" right="0.45" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="70" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -19762,28 +22813,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="172" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="163"/>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="163"/>
-      <c r="F1" s="163"/>
-      <c r="G1" s="164"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="174"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="167" t="s">
+      <c r="B2" s="177" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="168"/>
-      <c r="D2" s="169"/>
-      <c r="E2" s="167" t="s">
+      <c r="C2" s="178"/>
+      <c r="D2" s="179"/>
+      <c r="E2" s="177" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="168"/>
-      <c r="G2" s="169"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="179"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -20877,15 +23928,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="166" t="s">
+      <c r="A55" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="166"/>
-      <c r="C55" s="166"/>
-      <c r="D55" s="166"/>
-      <c r="E55" s="166"/>
-      <c r="F55" s="166"/>
-      <c r="G55" s="166"/>
+      <c r="B55" s="176"/>
+      <c r="C55" s="176"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -20913,26 +23964,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="177" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -21903,15 +24954,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="166" t="s">
+      <c r="A55" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="166"/>
-      <c r="C55" s="166"/>
-      <c r="D55" s="166"/>
-      <c r="E55" s="166"/>
-      <c r="F55" s="166"/>
-      <c r="G55" s="166"/>
+      <c r="B55" s="176"/>
+      <c r="C55" s="176"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -21940,28 +24991,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="177" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -22956,15 +26007,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="166" t="s">
+      <c r="A55" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="166"/>
-      <c r="C55" s="166"/>
-      <c r="D55" s="166"/>
-      <c r="E55" s="166"/>
-      <c r="F55" s="166"/>
-      <c r="G55" s="166"/>
+      <c r="B55" s="176"/>
+      <c r="C55" s="176"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
     </row>
     <row r="56" spans="1:7" ht="18">
       <c r="A56" s="71"/>
@@ -22996,28 +26047,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -24024,15 +27075,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="166" t="s">
+      <c r="A55" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="166"/>
-      <c r="C55" s="166"/>
-      <c r="D55" s="166"/>
-      <c r="E55" s="166"/>
-      <c r="F55" s="166"/>
-      <c r="G55" s="166"/>
+      <c r="B55" s="176"/>
+      <c r="C55" s="176"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
     </row>
     <row r="56" spans="1:7" ht="18">
       <c r="A56" s="71"/>
@@ -24067,28 +27118,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -25096,15 +28147,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="166" t="s">
+      <c r="A55" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="166"/>
-      <c r="C55" s="166"/>
-      <c r="D55" s="166"/>
-      <c r="E55" s="166"/>
-      <c r="F55" s="166"/>
-      <c r="G55" s="166"/>
+      <c r="B55" s="176"/>
+      <c r="C55" s="176"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -25137,28 +28188,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="177" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -26324,28 +29375,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="180" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">

--- a/gstdatabase/Gross_Net_Tax_collection.xlsx
+++ b/gstdatabase/Gross_Net_Tax_collection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CAADC9-1616-4F05-999F-DC8E0FDBE957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382A688B-369E-4DDE-9F5F-F20E0BDF9734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="17" activeTab="25" xr2:uid="{5CAD827C-DDF4-9F48-BEDE-38002A84F822}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="18" activeTab="23" xr2:uid="{5CAD827C-DDF4-9F48-BEDE-38002A84F822}"/>
   </bookViews>
   <sheets>
     <sheet name="Apr-24" sheetId="2" r:id="rId1"/>
@@ -39,6 +39,7 @@
     <sheet name="Mar_26" sheetId="25" r:id="rId24"/>
     <sheet name="Apr-26" sheetId="26" r:id="rId25"/>
     <sheet name="May-26" sheetId="27" r:id="rId26"/>
+    <sheet name="Jun-26" sheetId="28" r:id="rId27"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Apr-24'!$A$1:$G$52</definedName>
@@ -54,6 +55,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="15">'Jul-25'!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Jun-24'!$A$1:$G$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'Jun-25'!$A$1:$G$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="26">'Jun-26'!$A$1:$G$51</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="23">Mar_26!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'Mar-25'!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'May-24'!$A$1:$G$52</definedName>
@@ -86,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="140">
   <si>
     <t>Monthly</t>
   </si>
@@ -500,6 +502,12 @@
   </si>
   <si>
     <t>G = F/E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GST Gross and Net Collections as on 30/06/2026(Amount in crores) </t>
+  </si>
+  <si>
+    <t>Jun-25</t>
   </si>
 </sst>
 </file>
@@ -1574,9 +1582,6 @@
     <xf numFmtId="0" fontId="33" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1618,6 +1623,9 @@
     </xf>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1997,28 +2005,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="171" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="174"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="173"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -3150,15 +3158,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="176" t="s">
+      <c r="A55" s="175" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="176"/>
-      <c r="C55" s="176"/>
-      <c r="D55" s="176"/>
-      <c r="E55" s="176"/>
-      <c r="F55" s="176"/>
-      <c r="G55" s="176"/>
+      <c r="B55" s="175"/>
+      <c r="C55" s="175"/>
+      <c r="D55" s="175"/>
+      <c r="E55" s="175"/>
+      <c r="F55" s="175"/>
+      <c r="G55" s="175"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3192,36 +3200,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="179" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="178"/>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
-      <c r="I1" s="178"/>
-      <c r="J1" s="179"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
+      <c r="I1" s="177"/>
+      <c r="J1" s="178"/>
     </row>
     <row r="2" spans="1:12" ht="15.6">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="175" t="s">
+      <c r="C2" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175" t="s">
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174" t="s">
         <v>78</v>
       </c>
-      <c r="H2" s="175"/>
-      <c r="I2" s="175"/>
-      <c r="J2" s="175"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
     </row>
     <row r="3" spans="1:12" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -4814,33 +4822,33 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="18">
-      <c r="A54" s="182" t="s">
+      <c r="A54" s="181" t="s">
         <v>85</v>
       </c>
-      <c r="B54" s="182"/>
-      <c r="C54" s="182"/>
-      <c r="D54" s="182"/>
+      <c r="B54" s="181"/>
+      <c r="C54" s="181"/>
+      <c r="D54" s="181"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="183" t="s">
+      <c r="A55" s="182" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="183"/>
-      <c r="C55" s="183"/>
-      <c r="D55" s="183"/>
+      <c r="B55" s="182"/>
+      <c r="C55" s="182"/>
+      <c r="D55" s="182"/>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="B56" s="184" t="s">
+      <c r="B56" s="183" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="184"/>
-      <c r="D56" s="184"/>
+      <c r="C56" s="183"/>
+      <c r="D56" s="183"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="181" t="s">
+      <c r="A57" s="180" t="s">
         <v>88</v>
       </c>
       <c r="B57" s="100" t="s">
@@ -4849,19 +4857,19 @@
       <c r="C57" s="100" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="181" t="s">
+      <c r="D57" s="180" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="181"/>
+      <c r="A58" s="180"/>
       <c r="B58" s="100" t="s">
         <v>91</v>
       </c>
       <c r="C58" s="100" t="s">
         <v>91</v>
       </c>
-      <c r="D58" s="181"/>
+      <c r="D58" s="180"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="101" t="s">
@@ -5012,28 +5020,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="179" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="178"/>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="179"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="178"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -7094,7 +7102,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.6">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="184" t="s">
         <v>103</v>
       </c>
       <c r="B1" s="170"/>
@@ -8177,12 +8185,12 @@
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="171" t="s">
+      <c r="B2" s="185" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="168"/>
       <c r="D2" s="169"/>
-      <c r="E2" s="171" t="s">
+      <c r="E2" s="185" t="s">
         <v>78</v>
       </c>
       <c r="F2" s="168"/>
@@ -12351,7 +12359,7 @@
       </c>
       <c r="C2" s="170"/>
       <c r="D2" s="170"/>
-      <c r="E2" s="171" t="s">
+      <c r="E2" s="185" t="s">
         <v>78</v>
       </c>
       <c r="F2" s="168"/>
@@ -13418,7 +13426,7 @@
       </c>
       <c r="C2" s="170"/>
       <c r="D2" s="170"/>
-      <c r="E2" s="171" t="s">
+      <c r="E2" s="185" t="s">
         <v>78</v>
       </c>
       <c r="F2" s="168"/>
@@ -14457,28 +14465,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="171" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="174"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="173"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -15573,15 +15581,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="176" t="s">
+      <c r="A55" s="175" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="176"/>
-      <c r="C55" s="176"/>
-      <c r="D55" s="176"/>
-      <c r="E55" s="176"/>
-      <c r="F55" s="176"/>
-      <c r="G55" s="176"/>
+      <c r="B55" s="175"/>
+      <c r="C55" s="175"/>
+      <c r="D55" s="175"/>
+      <c r="E55" s="175"/>
+      <c r="F55" s="175"/>
+      <c r="G55" s="175"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -21867,7 +21875,7 @@
       </c>
       <c r="C2" s="170"/>
       <c r="D2" s="170"/>
-      <c r="E2" s="171" t="s">
+      <c r="E2" s="185" t="s">
         <v>78</v>
       </c>
       <c r="F2" s="168"/>
@@ -22788,6 +22796,964 @@
         <v>-253.81717899999995</v>
       </c>
       <c r="G51" s="66"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.45" right="0.45" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="70" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4FC2135-1C21-445F-9E21-07E0E786F3F2}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="38.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="6" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6">
+      <c r="A1" s="167" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.6">
+      <c r="A2" s="108"/>
+      <c r="B2" s="170" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.6">
+      <c r="A3" s="109" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="110" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="111">
+        <v>46174</v>
+      </c>
+      <c r="D3" s="109" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="110" t="s">
+        <v>139</v>
+      </c>
+      <c r="F3" s="111">
+        <v>46174</v>
+      </c>
+      <c r="G3" s="109" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6">
+      <c r="A4" s="109" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="109" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="109" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="109" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" collapsed="1">
+      <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="I5" s="22"/>
+    </row>
+    <row r="6" spans="1:11" outlineLevel="1">
+      <c r="A6" s="127" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="77">
+        <v>34557.658900000002</v>
+      </c>
+      <c r="C6" s="77">
+        <v>37375.85</v>
+      </c>
+      <c r="D6" s="150"/>
+      <c r="E6" s="67">
+        <v>118625.11</v>
+      </c>
+      <c r="F6" s="67">
+        <v>126913.13</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="128"/>
+    </row>
+    <row r="7" spans="1:11" outlineLevel="1">
+      <c r="A7" s="127" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="77">
+        <v>43267.864600000001</v>
+      </c>
+      <c r="C7" s="77">
+        <v>45116.31</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="67">
+        <v>146541.87</v>
+      </c>
+      <c r="F7" s="67">
+        <v>151590.10999999999</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="I7" s="128"/>
+    </row>
+    <row r="8" spans="1:11" outlineLevel="1">
+      <c r="A8" s="127" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="77">
+        <v>48680.200100000002</v>
+      </c>
+      <c r="C8" s="77">
+        <v>52281.99</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="67">
+        <v>176951.27</v>
+      </c>
+      <c r="F8" s="67">
+        <v>175923.42</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="138"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="136" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="118">
+        <v>126505.72360000001</v>
+      </c>
+      <c r="C9" s="35">
+        <v>134774.15</v>
+      </c>
+      <c r="D9" s="61">
+        <v>6.5360127589487504E-2</v>
+      </c>
+      <c r="E9" s="37">
+        <v>442118.25</v>
+      </c>
+      <c r="F9" s="37">
+        <v>454426.66000000003</v>
+      </c>
+      <c r="G9" s="61">
+        <v>2.7839633401245178E-2</v>
+      </c>
+      <c r="I9" s="22"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="14"/>
+      <c r="B10" s="118"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="9"/>
+      <c r="I10" s="22"/>
+    </row>
+    <row r="11" spans="1:11" ht="12.75" customHeight="1" collapsed="1">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="9"/>
+      <c r="I11" s="22"/>
+    </row>
+    <row r="12" spans="1:11" outlineLevel="1">
+      <c r="A12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="141">
+        <v>44599.519999999997</v>
+      </c>
+      <c r="C12" s="141">
+        <v>60038.301154890003</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="36">
+        <v>140423.72</v>
+      </c>
+      <c r="F12" s="36">
+        <v>177272.61115489001</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="I12" s="22"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="35">
+        <v>44599.519999999997</v>
+      </c>
+      <c r="C13" s="35">
+        <v>60038.301154890003</v>
+      </c>
+      <c r="D13" s="61">
+        <v>0.34616473798126091</v>
+      </c>
+      <c r="E13" s="35">
+        <v>140423.72</v>
+      </c>
+      <c r="F13" s="35">
+        <v>177272.61115489001</v>
+      </c>
+      <c r="G13" s="63">
+        <v>0.26241215625743286</v>
+      </c>
+      <c r="I13" s="48"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="9"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="113"/>
+      <c r="K14" s="22"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.6">
+      <c r="A15" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="75">
+        <v>34557.658900000002</v>
+      </c>
+      <c r="C15" s="65">
+        <v>37375.85</v>
+      </c>
+      <c r="D15" s="52"/>
+      <c r="E15" s="65">
+        <v>118625.11</v>
+      </c>
+      <c r="F15" s="65">
+        <v>126913.13</v>
+      </c>
+      <c r="G15" s="52"/>
+      <c r="I15" s="22"/>
+    </row>
+    <row r="16" spans="1:11" ht="15.6">
+      <c r="A16" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="75">
+        <v>43267.864600000001</v>
+      </c>
+      <c r="C16" s="65">
+        <v>45116.31</v>
+      </c>
+      <c r="D16" s="52"/>
+      <c r="E16" s="65">
+        <v>146541.87</v>
+      </c>
+      <c r="F16" s="65">
+        <v>151590.10999999999</v>
+      </c>
+      <c r="G16" s="52"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.6">
+      <c r="A17" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="75">
+        <v>93279.720100000006</v>
+      </c>
+      <c r="C17" s="65">
+        <v>112320.29115489</v>
+      </c>
+      <c r="D17" s="52"/>
+      <c r="E17" s="65">
+        <v>317374.99</v>
+      </c>
+      <c r="F17" s="65">
+        <v>353196.03115489002</v>
+      </c>
+      <c r="G17" s="52"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.6">
+      <c r="A18" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="40">
+        <v>171105.24360000002</v>
+      </c>
+      <c r="C18" s="40">
+        <v>194812.45115489</v>
+      </c>
+      <c r="D18" s="66">
+        <v>0.13855339062024052</v>
+      </c>
+      <c r="E18" s="40">
+        <v>582541.97</v>
+      </c>
+      <c r="F18" s="40">
+        <v>631699.27115489007</v>
+      </c>
+      <c r="G18" s="66">
+        <v>8.4384136571121315E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="20" customFormat="1" collapsed="1">
+      <c r="A19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="114"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="84"/>
+    </row>
+    <row r="20" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="77">
+        <v>3190.95</v>
+      </c>
+      <c r="C20" s="77">
+        <v>4378.7699999999995</v>
+      </c>
+      <c r="D20" s="11"/>
+      <c r="E20" s="41">
+        <v>10645.36</v>
+      </c>
+      <c r="F20" s="41">
+        <v>13744.4</v>
+      </c>
+      <c r="G20" s="12"/>
+    </row>
+    <row r="21" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A21" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="77">
+        <v>3870.5</v>
+      </c>
+      <c r="C21" s="77">
+        <v>5047.4400000000005</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="41">
+        <v>13087.61</v>
+      </c>
+      <c r="F21" s="41">
+        <v>16398.449999999997</v>
+      </c>
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="77">
+        <v>5370.93</v>
+      </c>
+      <c r="C22" s="77">
+        <v>8340.59</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="41">
+        <v>19423.27</v>
+      </c>
+      <c r="F22" s="41">
+        <v>24622.95</v>
+      </c>
+      <c r="G22" s="12"/>
+    </row>
+    <row r="23" spans="1:10" s="20" customFormat="1">
+      <c r="A23" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="78">
+        <v>12432.380000000001</v>
+      </c>
+      <c r="C23" s="35">
+        <v>17766.8</v>
+      </c>
+      <c r="D23" s="63">
+        <v>0.42907472261948221</v>
+      </c>
+      <c r="E23" s="35">
+        <v>43156.240000000005</v>
+      </c>
+      <c r="F23" s="35">
+        <v>54765.8</v>
+      </c>
+      <c r="G23" s="63">
+        <v>0.26901231432580763</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="20" customFormat="1" collapsed="1">
+      <c r="A24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="153"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="132"/>
+      <c r="G24" s="62"/>
+    </row>
+    <row r="25" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="77">
+        <v>12688.47</v>
+      </c>
+      <c r="C25" s="77">
+        <v>14668.778136700001</v>
+      </c>
+      <c r="D25" s="150"/>
+      <c r="E25" s="67">
+        <v>35198.339999999997</v>
+      </c>
+      <c r="F25" s="67">
+        <v>36715.958136700006</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="21"/>
+    </row>
+    <row r="26" spans="1:10" s="20" customFormat="1">
+      <c r="A26" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="35">
+        <v>12688.47</v>
+      </c>
+      <c r="C26" s="35">
+        <v>14668.778136700001</v>
+      </c>
+      <c r="D26" s="63">
+        <v>0.15607146777349845</v>
+      </c>
+      <c r="E26" s="35">
+        <v>35198.339999999997</v>
+      </c>
+      <c r="F26" s="35">
+        <v>36715.958136700006</v>
+      </c>
+      <c r="G26" s="63">
+        <v>4.3116184930880541E-2</v>
+      </c>
+      <c r="H26" s="21"/>
+      <c r="I26"/>
+      <c r="J26" s="81"/>
+    </row>
+    <row r="27" spans="1:10" s="20" customFormat="1">
+      <c r="A27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="21"/>
+      <c r="I27"/>
+    </row>
+    <row r="28" spans="1:10" s="20" customFormat="1">
+      <c r="A28" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="42">
+        <v>3190.95</v>
+      </c>
+      <c r="C28" s="42">
+        <v>4378.7699999999995</v>
+      </c>
+      <c r="D28" s="29"/>
+      <c r="E28" s="42">
+        <v>10645.36</v>
+      </c>
+      <c r="F28" s="42">
+        <v>13744.4</v>
+      </c>
+      <c r="G28" s="24"/>
+      <c r="H28" s="21"/>
+      <c r="I28"/>
+    </row>
+    <row r="29" spans="1:10" s="20" customFormat="1">
+      <c r="A29" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="42">
+        <v>3870.5</v>
+      </c>
+      <c r="C29" s="42">
+        <v>5047.4400000000005</v>
+      </c>
+      <c r="D29" s="29"/>
+      <c r="E29" s="42">
+        <v>13087.61</v>
+      </c>
+      <c r="F29" s="42">
+        <v>16398.449999999997</v>
+      </c>
+      <c r="G29" s="24"/>
+      <c r="H29" s="21"/>
+      <c r="I29"/>
+    </row>
+    <row r="30" spans="1:10" s="20" customFormat="1">
+      <c r="A30" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="42">
+        <v>18059.400000000001</v>
+      </c>
+      <c r="C30" s="42">
+        <v>23009.368136700003</v>
+      </c>
+      <c r="D30" s="29"/>
+      <c r="E30" s="42">
+        <v>54621.61</v>
+      </c>
+      <c r="F30" s="42">
+        <v>61338.908136700004</v>
+      </c>
+      <c r="G30" s="24"/>
+      <c r="H30" s="21"/>
+      <c r="I30"/>
+    </row>
+    <row r="31" spans="1:10" s="20" customFormat="1" ht="15.6">
+      <c r="A31" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="40">
+        <v>25120.850000000002</v>
+      </c>
+      <c r="C31" s="40">
+        <v>32435.578136700002</v>
+      </c>
+      <c r="D31" s="70">
+        <v>0.29118155383675304</v>
+      </c>
+      <c r="E31" s="40">
+        <v>78354.58</v>
+      </c>
+      <c r="F31" s="40">
+        <v>91481.758136699995</v>
+      </c>
+      <c r="G31" s="70">
+        <v>0.16753555614362292</v>
+      </c>
+      <c r="H31" s="21"/>
+      <c r="I31"/>
+    </row>
+    <row r="32" spans="1:10" s="20" customFormat="1">
+      <c r="A32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="132"/>
+      <c r="F32" s="132"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="21"/>
+      <c r="I32"/>
+    </row>
+    <row r="33" spans="1:9" s="20" customFormat="1">
+      <c r="A33" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="42">
+        <v>31366.708900000001</v>
+      </c>
+      <c r="C33" s="42">
+        <v>32997.08</v>
+      </c>
+      <c r="D33" s="28"/>
+      <c r="E33" s="42">
+        <v>107979.75</v>
+      </c>
+      <c r="F33" s="42">
+        <v>113168.73000000001</v>
+      </c>
+      <c r="G33" s="29"/>
+      <c r="H33" s="21"/>
+      <c r="I33"/>
+    </row>
+    <row r="34" spans="1:9" s="20" customFormat="1">
+      <c r="A34" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="42">
+        <v>39397.364600000001</v>
+      </c>
+      <c r="C34" s="42">
+        <v>40068.869999999995</v>
+      </c>
+      <c r="D34" s="28"/>
+      <c r="E34" s="42">
+        <v>133454.26</v>
+      </c>
+      <c r="F34" s="42">
+        <v>135191.65999999997</v>
+      </c>
+      <c r="G34" s="29"/>
+      <c r="H34" s="21"/>
+      <c r="I34"/>
+    </row>
+    <row r="35" spans="1:9" s="20" customFormat="1">
+      <c r="A35" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="42">
+        <v>43309.270100000002</v>
+      </c>
+      <c r="C35" s="42">
+        <v>43941.399999999994</v>
+      </c>
+      <c r="D35" s="28"/>
+      <c r="E35" s="42">
+        <v>157528</v>
+      </c>
+      <c r="F35" s="42">
+        <v>151300.47</v>
+      </c>
+      <c r="G35" s="29"/>
+      <c r="H35" s="21"/>
+      <c r="I35"/>
+    </row>
+    <row r="36" spans="1:9" s="20" customFormat="1">
+      <c r="A36" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="43">
+        <v>114073.34359999999</v>
+      </c>
+      <c r="C36" s="43">
+        <v>117007.34999999999</v>
+      </c>
+      <c r="D36" s="63">
+        <v>2.5720383044802508E-2</v>
+      </c>
+      <c r="E36" s="43">
+        <v>398962.01</v>
+      </c>
+      <c r="F36" s="43">
+        <v>399660.86</v>
+      </c>
+      <c r="G36" s="63">
+        <v>1.7516705412627953E-3</v>
+      </c>
+      <c r="H36" s="21"/>
+      <c r="I36"/>
+    </row>
+    <row r="37" spans="1:9" s="20" customFormat="1">
+      <c r="A37" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="35"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="132"/>
+      <c r="F37" s="132"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="21"/>
+      <c r="I37"/>
+    </row>
+    <row r="38" spans="1:9" s="20" customFormat="1">
+      <c r="A38" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="42">
+        <v>31911.049999999996</v>
+      </c>
+      <c r="C38" s="42">
+        <v>45369.523018190004</v>
+      </c>
+      <c r="D38" s="28"/>
+      <c r="E38" s="42">
+        <v>105225.38</v>
+      </c>
+      <c r="F38" s="42">
+        <v>140556.65301819</v>
+      </c>
+      <c r="G38" s="29"/>
+      <c r="H38" s="21"/>
+      <c r="I38"/>
+    </row>
+    <row r="39" spans="1:9" s="20" customFormat="1">
+      <c r="A39" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="43">
+        <v>31911.049999999996</v>
+      </c>
+      <c r="C39" s="43">
+        <v>45369.523018190004</v>
+      </c>
+      <c r="D39" s="63">
+        <v>0.42174961394846022</v>
+      </c>
+      <c r="E39" s="43">
+        <v>105225.38</v>
+      </c>
+      <c r="F39" s="43">
+        <v>140556.65301819</v>
+      </c>
+      <c r="G39" s="63">
+        <v>0.33576759730580208</v>
+      </c>
+      <c r="H39" s="21"/>
+      <c r="I39"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="132"/>
+      <c r="F40" s="132"/>
+      <c r="G40" s="9"/>
+    </row>
+    <row r="41" spans="1:9" ht="15.6">
+      <c r="A41" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="65">
+        <v>31366.708900000001</v>
+      </c>
+      <c r="C41" s="65">
+        <v>32997.08</v>
+      </c>
+      <c r="D41" s="57"/>
+      <c r="E41" s="65">
+        <v>107979.75</v>
+      </c>
+      <c r="F41" s="65">
+        <v>113168.73000000001</v>
+      </c>
+      <c r="G41" s="52"/>
+    </row>
+    <row r="42" spans="1:9" ht="15.6">
+      <c r="A42" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="65">
+        <v>39397.364600000001</v>
+      </c>
+      <c r="C42" s="65">
+        <v>40068.869999999995</v>
+      </c>
+      <c r="D42" s="52"/>
+      <c r="E42" s="65">
+        <v>133454.26</v>
+      </c>
+      <c r="F42" s="65">
+        <v>135191.65999999997</v>
+      </c>
+      <c r="G42" s="52"/>
+    </row>
+    <row r="43" spans="1:9" ht="15.6">
+      <c r="A43" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="65">
+        <v>75220.320099999997</v>
+      </c>
+      <c r="C43" s="65">
+        <v>89310.923018189991</v>
+      </c>
+      <c r="D43" s="52"/>
+      <c r="E43" s="65">
+        <v>262753.38</v>
+      </c>
+      <c r="F43" s="65">
+        <v>291857.12301819003</v>
+      </c>
+      <c r="G43" s="52"/>
+    </row>
+    <row r="44" spans="1:9" ht="15.6">
+      <c r="A44" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" s="40">
+        <v>145984.39360000001</v>
+      </c>
+      <c r="C44" s="40">
+        <v>162376.87301818997</v>
+      </c>
+      <c r="D44" s="66">
+        <v>0.11228928667092397</v>
+      </c>
+      <c r="E44" s="40">
+        <v>504187.39</v>
+      </c>
+      <c r="F44" s="40">
+        <v>540217.51301819005</v>
+      </c>
+      <c r="G44" s="66">
+        <v>7.1461769438918354E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="B45" s="58"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="74"/>
+      <c r="E45" s="85"/>
+      <c r="F45" s="85"/>
+      <c r="G45" s="74"/>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="B46" s="58"/>
+      <c r="C46" s="58"/>
+      <c r="E46" s="85"/>
+      <c r="F46" s="85"/>
+    </row>
+    <row r="47" spans="1:9" ht="15.6">
+      <c r="A47" s="163" t="s">
+        <v>129</v>
+      </c>
+      <c r="B47" s="58"/>
+      <c r="C47" s="58"/>
+      <c r="E47" s="85"/>
+      <c r="F47" s="85"/>
+    </row>
+    <row r="48" spans="1:9" ht="15.6">
+      <c r="A48" s="164" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="34">
+        <v>12400.293399999999</v>
+      </c>
+      <c r="C48" s="34">
+        <v>103.91</v>
+      </c>
+      <c r="D48" s="91"/>
+      <c r="E48" s="34">
+        <v>36375.82</v>
+      </c>
+      <c r="F48" s="34">
+        <v>215.21</v>
+      </c>
+      <c r="G48" s="91"/>
+    </row>
+    <row r="49" spans="1:7" ht="15.6">
+      <c r="A49" s="164" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" s="34">
+        <v>1090.98</v>
+      </c>
+      <c r="C49" s="34">
+        <v>0.24336829999999998</v>
+      </c>
+      <c r="D49" s="91"/>
+      <c r="E49" s="34">
+        <v>3445.56</v>
+      </c>
+      <c r="F49" s="34">
+        <v>0.3233683</v>
+      </c>
+      <c r="G49" s="91"/>
+    </row>
+    <row r="50" spans="1:7" ht="15.6">
+      <c r="A50" s="164" t="s">
+        <v>132</v>
+      </c>
+      <c r="B50" s="34">
+        <v>-362.96999999999997</v>
+      </c>
+      <c r="C50" s="34">
+        <v>-104.99465610000001</v>
+      </c>
+      <c r="D50" s="91"/>
+      <c r="E50" s="34">
+        <v>-1469.15</v>
+      </c>
+      <c r="F50" s="34">
+        <v>-470.19465610000003</v>
+      </c>
+      <c r="G50" s="91"/>
+    </row>
+    <row r="51" spans="1:7" ht="15.6">
+      <c r="A51" s="165" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" s="40">
+        <v>13128.303399999999</v>
+      </c>
+      <c r="C51" s="40">
+        <v>-0.84128780000001768</v>
+      </c>
+      <c r="D51" s="96"/>
+      <c r="E51" s="40">
+        <v>38352.229999999996</v>
+      </c>
+      <c r="F51" s="40">
+        <v>-254.66128780000003</v>
+      </c>
+      <c r="G51" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -22813,28 +23779,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="171" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="174"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="173"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="176" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="178"/>
-      <c r="D2" s="179"/>
-      <c r="E2" s="177" t="s">
+      <c r="C2" s="177"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="176" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="178"/>
-      <c r="G2" s="179"/>
+      <c r="F2" s="177"/>
+      <c r="G2" s="178"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -23928,15 +24894,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="176" t="s">
+      <c r="A55" s="175" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="176"/>
-      <c r="C55" s="176"/>
-      <c r="D55" s="176"/>
-      <c r="E55" s="176"/>
-      <c r="F55" s="176"/>
-      <c r="G55" s="176"/>
+      <c r="B55" s="175"/>
+      <c r="C55" s="175"/>
+      <c r="D55" s="175"/>
+      <c r="E55" s="175"/>
+      <c r="F55" s="175"/>
+      <c r="G55" s="175"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -23964,26 +24930,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="176" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="178"/>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="179"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="178"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -24954,15 +25920,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="176" t="s">
+      <c r="A55" s="175" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="176"/>
-      <c r="C55" s="176"/>
-      <c r="D55" s="176"/>
-      <c r="E55" s="176"/>
-      <c r="F55" s="176"/>
-      <c r="G55" s="176"/>
+      <c r="B55" s="175"/>
+      <c r="C55" s="175"/>
+      <c r="D55" s="175"/>
+      <c r="E55" s="175"/>
+      <c r="F55" s="175"/>
+      <c r="G55" s="175"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -24991,28 +25957,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="176" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="178"/>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="179"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="178"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -26007,15 +26973,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="176" t="s">
+      <c r="A55" s="175" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="176"/>
-      <c r="C55" s="176"/>
-      <c r="D55" s="176"/>
-      <c r="E55" s="176"/>
-      <c r="F55" s="176"/>
-      <c r="G55" s="176"/>
+      <c r="B55" s="175"/>
+      <c r="C55" s="175"/>
+      <c r="D55" s="175"/>
+      <c r="E55" s="175"/>
+      <c r="F55" s="175"/>
+      <c r="G55" s="175"/>
     </row>
     <row r="56" spans="1:7" ht="18">
       <c r="A56" s="71"/>
@@ -26047,28 +27013,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="176" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="178"/>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="179"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="178"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -27075,15 +28041,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="176" t="s">
+      <c r="A55" s="175" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="176"/>
-      <c r="C55" s="176"/>
-      <c r="D55" s="176"/>
-      <c r="E55" s="176"/>
-      <c r="F55" s="176"/>
-      <c r="G55" s="176"/>
+      <c r="B55" s="175"/>
+      <c r="C55" s="175"/>
+      <c r="D55" s="175"/>
+      <c r="E55" s="175"/>
+      <c r="F55" s="175"/>
+      <c r="G55" s="175"/>
     </row>
     <row r="56" spans="1:7" ht="18">
       <c r="A56" s="71"/>
@@ -27118,28 +28084,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="176" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="178"/>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="179"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="178"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -28147,15 +29113,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="176" t="s">
+      <c r="A55" s="175" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="176"/>
-      <c r="C55" s="176"/>
-      <c r="D55" s="176"/>
-      <c r="E55" s="176"/>
-      <c r="F55" s="176"/>
-      <c r="G55" s="176"/>
+      <c r="B55" s="175"/>
+      <c r="C55" s="175"/>
+      <c r="D55" s="175"/>
+      <c r="E55" s="175"/>
+      <c r="F55" s="175"/>
+      <c r="G55" s="175"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -28188,28 +29154,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="176" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="178"/>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="179"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="178"/>
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -29375,28 +30341,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="179" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="178"/>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="179"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="178"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">

--- a/gstdatabase/Gross_Net_Tax_collection.xlsx
+++ b/gstdatabase/Gross_Net_Tax_collection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382A688B-369E-4DDE-9F5F-F20E0BDF9734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3FB212-7C2A-405B-9BB1-398AA4CEDC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="18" activeTab="23" xr2:uid="{5CAD827C-DDF4-9F48-BEDE-38002A84F822}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="19" activeTab="27" xr2:uid="{5CAD827C-DDF4-9F48-BEDE-38002A84F822}"/>
   </bookViews>
   <sheets>
     <sheet name="Apr-24" sheetId="2" r:id="rId1"/>
@@ -40,6 +40,7 @@
     <sheet name="Apr-26" sheetId="26" r:id="rId25"/>
     <sheet name="May-26" sheetId="27" r:id="rId26"/>
     <sheet name="Jun-26" sheetId="28" r:id="rId27"/>
+    <sheet name="Jul-26" sheetId="30" r:id="rId28"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Apr-24'!$A$1:$G$52</definedName>
@@ -53,6 +54,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="21">'Jan-26'!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Jul-24'!$A$1:$G$55</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'Jul-25'!$A$1:$G$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="27">'Jul-26'!$A$1:$G$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Jun-24'!$A$1:$G$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'Jun-25'!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="26">'Jun-26'!$A$1:$G$51</definedName>
@@ -88,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="141">
   <si>
     <t>Monthly</t>
   </si>
@@ -508,6 +510,9 @@
   </si>
   <si>
     <t>Jun-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GST Gross and Net Collections as on  31/07/2026 (Amount in crores) </t>
   </si>
 </sst>
 </file>
@@ -1250,7 +1255,7 @@
     <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1570,16 +1575,16 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1591,23 +1596,11 @@
     <xf numFmtId="0" fontId="25" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="38" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1619,6 +1612,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1635,6 +1640,9 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -2017,16 +2025,16 @@
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -3158,15 +3166,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="175" t="s">
+      <c r="A55" s="174" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="175"/>
-      <c r="C55" s="175"/>
-      <c r="D55" s="175"/>
-      <c r="E55" s="175"/>
-      <c r="F55" s="175"/>
-      <c r="G55" s="175"/>
+      <c r="B55" s="174"/>
+      <c r="C55" s="174"/>
+      <c r="D55" s="174"/>
+      <c r="E55" s="174"/>
+      <c r="F55" s="174"/>
+      <c r="G55" s="174"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3200,36 +3208,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="167" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
-      <c r="J1" s="178"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="168"/>
+      <c r="H1" s="168"/>
+      <c r="I1" s="168"/>
+      <c r="J1" s="169"/>
     </row>
     <row r="2" spans="1:12" ht="15.6">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="174" t="s">
+      <c r="C2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174"/>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174" t="s">
+      <c r="D2" s="170"/>
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170" t="s">
         <v>78</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="170"/>
+      <c r="J2" s="170"/>
     </row>
     <row r="3" spans="1:12" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -4822,33 +4830,33 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="18">
-      <c r="A54" s="181" t="s">
+      <c r="A54" s="177" t="s">
         <v>85</v>
       </c>
-      <c r="B54" s="181"/>
-      <c r="C54" s="181"/>
-      <c r="D54" s="181"/>
+      <c r="B54" s="177"/>
+      <c r="C54" s="177"/>
+      <c r="D54" s="177"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="182" t="s">
+      <c r="A55" s="178" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="182"/>
-      <c r="C55" s="182"/>
-      <c r="D55" s="182"/>
+      <c r="B55" s="178"/>
+      <c r="C55" s="178"/>
+      <c r="D55" s="178"/>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="B56" s="183" t="s">
+      <c r="B56" s="179" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="183"/>
-      <c r="D56" s="183"/>
+      <c r="C56" s="179"/>
+      <c r="D56" s="179"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="180" t="s">
+      <c r="A57" s="176" t="s">
         <v>88</v>
       </c>
       <c r="B57" s="100" t="s">
@@ -4857,19 +4865,19 @@
       <c r="C57" s="100" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="180" t="s">
+      <c r="D57" s="176" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="180"/>
+      <c r="A58" s="176"/>
       <c r="B58" s="100" t="s">
         <v>91</v>
       </c>
       <c r="C58" s="100" t="s">
         <v>91</v>
       </c>
-      <c r="D58" s="180"/>
+      <c r="D58" s="176"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="101" t="s">
@@ -5020,28 +5028,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="167" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="178"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -6040,28 +6048,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -7105,25 +7113,25 @@
       <c r="A1" s="184" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
     </row>
     <row r="2" spans="1:13" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
     </row>
     <row r="3" spans="1:13" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -8173,28 +8181,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
       <c r="B2" s="185" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="168"/>
-      <c r="D2" s="169"/>
+      <c r="C2" s="181"/>
+      <c r="D2" s="182"/>
       <c r="E2" s="185" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="168"/>
-      <c r="G2" s="169"/>
+      <c r="F2" s="181"/>
+      <c r="G2" s="182"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -9229,28 +9237,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -10249,28 +10257,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -11276,28 +11284,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -12342,28 +12350,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
       <c r="E2" s="185" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="168"/>
-      <c r="G2" s="169"/>
+      <c r="F2" s="181"/>
+      <c r="G2" s="182"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -13409,28 +13417,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
       <c r="E2" s="185" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="168"/>
-      <c r="G2" s="169"/>
+      <c r="F2" s="181"/>
+      <c r="G2" s="182"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -14477,16 +14485,16 @@
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -15581,15 +15589,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="175" t="s">
+      <c r="A55" s="174" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="175"/>
-      <c r="C55" s="175"/>
-      <c r="D55" s="175"/>
-      <c r="E55" s="175"/>
-      <c r="F55" s="175"/>
-      <c r="G55" s="175"/>
+      <c r="B55" s="174"/>
+      <c r="C55" s="174"/>
+      <c r="D55" s="174"/>
+      <c r="E55" s="174"/>
+      <c r="F55" s="174"/>
+      <c r="G55" s="174"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -15621,15 +15629,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
@@ -16688,28 +16696,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -17735,28 +17743,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -18797,28 +18805,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -19863,28 +19871,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -20902,28 +20910,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -21858,28 +21866,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
       <c r="E2" s="185" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="168"/>
-      <c r="G2" s="169"/>
+      <c r="F2" s="181"/>
+      <c r="G2" s="182"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -22828,28 +22836,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -23763,6 +23771,872 @@
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="70" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D269D10-5D90-48D4-8721-416ABBEDD123}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K45"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="38.44140625" customWidth="1"/>
+    <col min="2" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="6" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A1" s="180" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="182"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.6">
+      <c r="A2" s="108"/>
+      <c r="B2" s="183" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.6">
+      <c r="A3" s="109" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="111">
+        <v>45839</v>
+      </c>
+      <c r="C3" s="111">
+        <v>46204</v>
+      </c>
+      <c r="D3" s="109" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="111">
+        <v>45839</v>
+      </c>
+      <c r="F3" s="111">
+        <v>46204</v>
+      </c>
+      <c r="G3" s="109" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6">
+      <c r="A4" s="109" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="109" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="109" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="109" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="109" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" collapsed="1">
+      <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="I5" s="22"/>
+    </row>
+    <row r="6" spans="1:11" outlineLevel="1">
+      <c r="A6" s="127" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="77">
+        <v>35469.994099999996</v>
+      </c>
+      <c r="C6" s="77">
+        <v>39834.639999999999</v>
+      </c>
+      <c r="D6" s="150"/>
+      <c r="E6" s="67">
+        <v>154095.10999999999</v>
+      </c>
+      <c r="F6" s="67">
+        <v>166747.76999999999</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="128"/>
+    </row>
+    <row r="7" spans="1:11" outlineLevel="1">
+      <c r="A7" s="127" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="77">
+        <v>44059.178700000004</v>
+      </c>
+      <c r="C7" s="77">
+        <v>47880.94</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="67">
+        <v>190601.05</v>
+      </c>
+      <c r="F7" s="67">
+        <v>199471.05</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="I7" s="128"/>
+    </row>
+    <row r="8" spans="1:11" outlineLevel="1">
+      <c r="A8" s="127" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="77">
+        <v>51910.215199999999</v>
+      </c>
+      <c r="C8" s="77">
+        <v>56979.19</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="67">
+        <v>228861.49</v>
+      </c>
+      <c r="F8" s="67">
+        <v>232902.61</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="138"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="136" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="35">
+        <v>131439.38800000001</v>
+      </c>
+      <c r="C9" s="35">
+        <v>144694.77000000002</v>
+      </c>
+      <c r="D9" s="61">
+        <v>0.10084786761180009</v>
+      </c>
+      <c r="E9" s="37">
+        <v>573557.64999999991</v>
+      </c>
+      <c r="F9" s="37">
+        <v>599121.42999999993</v>
+      </c>
+      <c r="G9" s="61">
+        <v>4.4570550144349186E-2</v>
+      </c>
+      <c r="I9" s="22"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="14"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="61"/>
+      <c r="I10" s="22"/>
+    </row>
+    <row r="11" spans="1:11" ht="12.75" customHeight="1" collapsed="1">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="61"/>
+      <c r="I11" s="22"/>
+    </row>
+    <row r="12" spans="1:11" outlineLevel="1">
+      <c r="A12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="141">
+        <v>51625.85</v>
+      </c>
+      <c r="C12" s="141">
+        <v>66510.611412290003</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="36">
+        <v>192049.56999999998</v>
+      </c>
+      <c r="F12" s="36">
+        <v>243783.22141229</v>
+      </c>
+      <c r="G12" s="80"/>
+      <c r="I12" s="22"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="35">
+        <v>51625.85</v>
+      </c>
+      <c r="C13" s="35">
+        <v>66510.611412290003</v>
+      </c>
+      <c r="D13" s="61">
+        <v>0.28831992911090087</v>
+      </c>
+      <c r="E13" s="35">
+        <v>192049.56999999998</v>
+      </c>
+      <c r="F13" s="35">
+        <v>243783.22141229</v>
+      </c>
+      <c r="G13" s="63">
+        <v>0.26937655425258189</v>
+      </c>
+      <c r="I13" s="48"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="61"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="113"/>
+      <c r="K14" s="22"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.6">
+      <c r="A15" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="65">
+        <v>35469.994099999996</v>
+      </c>
+      <c r="C15" s="65">
+        <v>39834.639999999999</v>
+      </c>
+      <c r="D15" s="52"/>
+      <c r="E15" s="65">
+        <v>154095.10999999999</v>
+      </c>
+      <c r="F15" s="65">
+        <v>166747.76999999999</v>
+      </c>
+      <c r="G15" s="76"/>
+      <c r="I15" s="22"/>
+    </row>
+    <row r="16" spans="1:11" ht="15.6">
+      <c r="A16" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="65">
+        <v>44059.178700000004</v>
+      </c>
+      <c r="C16" s="65">
+        <v>47880.94</v>
+      </c>
+      <c r="D16" s="52"/>
+      <c r="E16" s="65">
+        <v>190601.05</v>
+      </c>
+      <c r="F16" s="65">
+        <v>199471.05</v>
+      </c>
+      <c r="G16" s="76"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.6">
+      <c r="A17" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="65">
+        <v>103536.0652</v>
+      </c>
+      <c r="C17" s="65">
+        <v>123489.80141229001</v>
+      </c>
+      <c r="D17" s="52"/>
+      <c r="E17" s="65">
+        <v>420911.05999999994</v>
+      </c>
+      <c r="F17" s="65">
+        <v>476685.83141228999</v>
+      </c>
+      <c r="G17" s="76"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.6">
+      <c r="A18" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="40">
+        <v>183065.23800000001</v>
+      </c>
+      <c r="C18" s="40">
+        <v>211205.38141229001</v>
+      </c>
+      <c r="D18" s="66">
+        <v>0.15371647681298173</v>
+      </c>
+      <c r="E18" s="40">
+        <v>765607.22</v>
+      </c>
+      <c r="F18" s="40">
+        <v>842904.65141228994</v>
+      </c>
+      <c r="G18" s="66">
+        <v>0.10096225504807799</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="20" customFormat="1" collapsed="1">
+      <c r="A19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="104"/>
+    </row>
+    <row r="20" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="77">
+        <v>3309.13</v>
+      </c>
+      <c r="C20" s="77">
+        <v>4100.71</v>
+      </c>
+      <c r="D20" s="79"/>
+      <c r="E20" s="41">
+        <v>13954.48</v>
+      </c>
+      <c r="F20" s="41">
+        <v>17844.77</v>
+      </c>
+      <c r="G20" s="80"/>
+    </row>
+    <row r="21" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A21" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="77">
+        <v>4532.7199999999993</v>
+      </c>
+      <c r="C21" s="77">
+        <v>4908.3899999999994</v>
+      </c>
+      <c r="D21" s="79"/>
+      <c r="E21" s="41">
+        <v>17620.32</v>
+      </c>
+      <c r="F21" s="41">
+        <v>21305.22</v>
+      </c>
+      <c r="G21" s="80"/>
+    </row>
+    <row r="22" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="77">
+        <v>8638.77</v>
+      </c>
+      <c r="C22" s="77">
+        <v>8670.93</v>
+      </c>
+      <c r="D22" s="79"/>
+      <c r="E22" s="41">
+        <v>28062.030000000002</v>
+      </c>
+      <c r="F22" s="41">
+        <v>33293.699999999997</v>
+      </c>
+      <c r="G22" s="80"/>
+    </row>
+    <row r="23" spans="1:10" s="20" customFormat="1">
+      <c r="A23" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="35">
+        <v>16480.62</v>
+      </c>
+      <c r="C23" s="35">
+        <v>17680.03</v>
+      </c>
+      <c r="D23" s="63">
+        <v>7.2776995040235049E-2</v>
+      </c>
+      <c r="E23" s="35">
+        <v>59636.83</v>
+      </c>
+      <c r="F23" s="35">
+        <v>72443.69</v>
+      </c>
+      <c r="G23" s="63">
+        <v>0.21474749747764932</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="20" customFormat="1" collapsed="1">
+      <c r="A24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="132"/>
+      <c r="G24" s="79"/>
+    </row>
+    <row r="25" spans="1:10" s="20" customFormat="1" outlineLevel="1">
+      <c r="A25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="77">
+        <v>10014.2847836</v>
+      </c>
+      <c r="C25" s="77">
+        <v>12288.0448048</v>
+      </c>
+      <c r="D25" s="189"/>
+      <c r="E25" s="67">
+        <v>45212.624783599997</v>
+      </c>
+      <c r="F25" s="67">
+        <v>49004.004804800003</v>
+      </c>
+      <c r="G25" s="80"/>
+      <c r="H25" s="21"/>
+    </row>
+    <row r="26" spans="1:10" s="20" customFormat="1">
+      <c r="A26" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="35">
+        <v>10014.2847836</v>
+      </c>
+      <c r="C26" s="35">
+        <v>12288.0448048</v>
+      </c>
+      <c r="D26" s="63">
+        <v>0.22705166373175723</v>
+      </c>
+      <c r="E26" s="35">
+        <v>45212.624783599997</v>
+      </c>
+      <c r="F26" s="35">
+        <v>49004.004804800003</v>
+      </c>
+      <c r="G26" s="63">
+        <v>8.3856667011627639E-2</v>
+      </c>
+      <c r="H26" s="21"/>
+      <c r="I26"/>
+      <c r="J26" s="81"/>
+    </row>
+    <row r="27" spans="1:10" s="20" customFormat="1">
+      <c r="A27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="21"/>
+      <c r="I27"/>
+    </row>
+    <row r="28" spans="1:10" s="20" customFormat="1">
+      <c r="A28" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="42">
+        <v>3309.13</v>
+      </c>
+      <c r="C28" s="42">
+        <v>4100.71</v>
+      </c>
+      <c r="D28" s="82"/>
+      <c r="E28" s="42">
+        <v>13954.48</v>
+      </c>
+      <c r="F28" s="42">
+        <v>17844.77</v>
+      </c>
+      <c r="G28" s="63"/>
+      <c r="H28" s="21"/>
+      <c r="I28"/>
+    </row>
+    <row r="29" spans="1:10" s="20" customFormat="1">
+      <c r="A29" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="42">
+        <v>4532.7199999999993</v>
+      </c>
+      <c r="C29" s="42">
+        <v>4908.3899999999994</v>
+      </c>
+      <c r="D29" s="82"/>
+      <c r="E29" s="42">
+        <v>17620.32</v>
+      </c>
+      <c r="F29" s="42">
+        <v>21305.22</v>
+      </c>
+      <c r="G29" s="63"/>
+      <c r="H29" s="21"/>
+      <c r="I29"/>
+    </row>
+    <row r="30" spans="1:10" s="20" customFormat="1">
+      <c r="A30" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="42">
+        <v>18653.054783600001</v>
+      </c>
+      <c r="C30" s="42">
+        <v>20958.9748048</v>
+      </c>
+      <c r="D30" s="82"/>
+      <c r="E30" s="42">
+        <v>73274.654783599995</v>
+      </c>
+      <c r="F30" s="42">
+        <v>82297.7048048</v>
+      </c>
+      <c r="G30" s="63"/>
+      <c r="H30" s="21"/>
+      <c r="I30"/>
+    </row>
+    <row r="31" spans="1:10" s="20" customFormat="1" ht="15.6">
+      <c r="A31" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="40">
+        <v>26494.904783599999</v>
+      </c>
+      <c r="C31" s="40">
+        <v>29968.074804799999</v>
+      </c>
+      <c r="D31" s="70">
+        <v>0.13108822430454059</v>
+      </c>
+      <c r="E31" s="40">
+        <v>104849.4547836</v>
+      </c>
+      <c r="F31" s="40">
+        <v>121447.6948048</v>
+      </c>
+      <c r="G31" s="70">
+        <v>0.15830544904079202</v>
+      </c>
+      <c r="H31" s="21"/>
+      <c r="I31"/>
+    </row>
+    <row r="32" spans="1:10" s="20" customFormat="1">
+      <c r="A32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="132"/>
+      <c r="F32" s="132"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="21"/>
+      <c r="I32"/>
+    </row>
+    <row r="33" spans="1:9" s="20" customFormat="1">
+      <c r="A33" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="42">
+        <v>32160.864099999995</v>
+      </c>
+      <c r="C33" s="42">
+        <v>35733.93</v>
+      </c>
+      <c r="D33" s="28"/>
+      <c r="E33" s="42">
+        <v>140140.62999999998</v>
+      </c>
+      <c r="F33" s="42">
+        <v>148903</v>
+      </c>
+      <c r="G33" s="82"/>
+      <c r="H33" s="21"/>
+      <c r="I33"/>
+    </row>
+    <row r="34" spans="1:9" s="20" customFormat="1">
+      <c r="A34" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="42">
+        <v>39526.458700000003</v>
+      </c>
+      <c r="C34" s="42">
+        <v>42972.55</v>
+      </c>
+      <c r="D34" s="28"/>
+      <c r="E34" s="42">
+        <v>172980.72999999998</v>
+      </c>
+      <c r="F34" s="42">
+        <v>178165.83</v>
+      </c>
+      <c r="G34" s="82"/>
+      <c r="H34" s="21"/>
+      <c r="I34"/>
+    </row>
+    <row r="35" spans="1:9" s="20" customFormat="1">
+      <c r="A35" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="42">
+        <v>43271.445200000002</v>
+      </c>
+      <c r="C35" s="42">
+        <v>48308.26</v>
+      </c>
+      <c r="D35" s="28"/>
+      <c r="E35" s="42">
+        <v>200799.46</v>
+      </c>
+      <c r="F35" s="42">
+        <v>199608.90999999997</v>
+      </c>
+      <c r="G35" s="82"/>
+      <c r="H35" s="21"/>
+      <c r="I35"/>
+    </row>
+    <row r="36" spans="1:9" s="20" customFormat="1">
+      <c r="A36" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="43">
+        <v>114958.768</v>
+      </c>
+      <c r="C36" s="43">
+        <v>127014.74000000002</v>
+      </c>
+      <c r="D36" s="63">
+        <v>0.10487213989628019</v>
+      </c>
+      <c r="E36" s="43">
+        <v>513920.81999999995</v>
+      </c>
+      <c r="F36" s="43">
+        <v>526677.74</v>
+      </c>
+      <c r="G36" s="63">
+        <v>2.4822734365967269E-2</v>
+      </c>
+      <c r="H36" s="21"/>
+      <c r="I36"/>
+    </row>
+    <row r="37" spans="1:9" s="20" customFormat="1">
+      <c r="A37" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="35"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="132"/>
+      <c r="F37" s="132"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="21"/>
+      <c r="I37"/>
+    </row>
+    <row r="38" spans="1:9" s="20" customFormat="1">
+      <c r="A38" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="42">
+        <v>41611.565216399998</v>
+      </c>
+      <c r="C38" s="42">
+        <v>54222.566607490007</v>
+      </c>
+      <c r="D38" s="28"/>
+      <c r="E38" s="42">
+        <v>146836.94521639997</v>
+      </c>
+      <c r="F38" s="42">
+        <v>194779.21660749</v>
+      </c>
+      <c r="G38" s="82"/>
+      <c r="H38" s="21"/>
+      <c r="I38"/>
+    </row>
+    <row r="39" spans="1:9" s="20" customFormat="1">
+      <c r="A39" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="43">
+        <v>41611.565216399998</v>
+      </c>
+      <c r="C39" s="43">
+        <v>54222.566607490007</v>
+      </c>
+      <c r="D39" s="63">
+        <v>0.30306481684855591</v>
+      </c>
+      <c r="E39" s="43">
+        <v>146836.94521639997</v>
+      </c>
+      <c r="F39" s="43">
+        <v>194779.21660749</v>
+      </c>
+      <c r="G39" s="63">
+        <v>0.32650005978015573</v>
+      </c>
+      <c r="H39" s="21"/>
+      <c r="I39"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="61"/>
+      <c r="E40" s="132"/>
+      <c r="F40" s="132"/>
+      <c r="G40" s="9"/>
+    </row>
+    <row r="41" spans="1:9" ht="15.6">
+      <c r="A41" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="65">
+        <v>32160.864099999995</v>
+      </c>
+      <c r="C41" s="65">
+        <v>35733.93</v>
+      </c>
+      <c r="D41" s="135"/>
+      <c r="E41" s="65">
+        <v>140140.62999999998</v>
+      </c>
+      <c r="F41" s="65">
+        <v>148903</v>
+      </c>
+      <c r="G41" s="52"/>
+    </row>
+    <row r="42" spans="1:9" ht="15.6">
+      <c r="A42" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="65">
+        <v>39526.458700000003</v>
+      </c>
+      <c r="C42" s="65">
+        <v>42972.55</v>
+      </c>
+      <c r="D42" s="76"/>
+      <c r="E42" s="65">
+        <v>172980.72999999998</v>
+      </c>
+      <c r="F42" s="65">
+        <v>178165.83</v>
+      </c>
+      <c r="G42" s="52"/>
+    </row>
+    <row r="43" spans="1:9" ht="15.6">
+      <c r="A43" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="65">
+        <v>84883.010416400008</v>
+      </c>
+      <c r="C43" s="65">
+        <v>102530.82660749002</v>
+      </c>
+      <c r="D43" s="76"/>
+      <c r="E43" s="65">
+        <v>347636.40521639993</v>
+      </c>
+      <c r="F43" s="65">
+        <v>394388.12660749</v>
+      </c>
+      <c r="G43" s="52"/>
+    </row>
+    <row r="44" spans="1:9" ht="15.6">
+      <c r="A44" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" s="40">
+        <v>156570.3332164</v>
+      </c>
+      <c r="C44" s="40">
+        <v>181237.30660749003</v>
+      </c>
+      <c r="D44" s="66">
+        <v>0.15754564025227658</v>
+      </c>
+      <c r="E44" s="40">
+        <v>660757.76521639992</v>
+      </c>
+      <c r="F44" s="40">
+        <v>721456.95660748996</v>
+      </c>
+      <c r="G44" s="66">
+        <v>9.186300121832236E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="74"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.45" right="0.45" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="67" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -23791,16 +24665,16 @@
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="176" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="177"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="176" t="s">
+      <c r="C2" s="168"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="175" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="177"/>
-      <c r="G2" s="178"/>
+      <c r="F2" s="168"/>
+      <c r="G2" s="169"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -24894,15 +25768,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="175" t="s">
+      <c r="A55" s="174" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="175"/>
-      <c r="C55" s="175"/>
-      <c r="D55" s="175"/>
-      <c r="E55" s="175"/>
-      <c r="F55" s="175"/>
-      <c r="G55" s="175"/>
+      <c r="B55" s="174"/>
+      <c r="C55" s="174"/>
+      <c r="D55" s="174"/>
+      <c r="E55" s="174"/>
+      <c r="F55" s="174"/>
+      <c r="G55" s="174"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -24930,26 +25804,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="175" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="178"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174"/>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -25920,15 +26794,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="175" t="s">
+      <c r="A55" s="174" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="175"/>
-      <c r="C55" s="175"/>
-      <c r="D55" s="175"/>
-      <c r="E55" s="175"/>
-      <c r="F55" s="175"/>
-      <c r="G55" s="175"/>
+      <c r="B55" s="174"/>
+      <c r="C55" s="174"/>
+      <c r="D55" s="174"/>
+      <c r="E55" s="174"/>
+      <c r="F55" s="174"/>
+      <c r="G55" s="174"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -25957,28 +26831,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="175" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="178"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -26973,15 +27847,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="175" t="s">
+      <c r="A55" s="174" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="175"/>
-      <c r="C55" s="175"/>
-      <c r="D55" s="175"/>
-      <c r="E55" s="175"/>
-      <c r="F55" s="175"/>
-      <c r="G55" s="175"/>
+      <c r="B55" s="174"/>
+      <c r="C55" s="174"/>
+      <c r="D55" s="174"/>
+      <c r="E55" s="174"/>
+      <c r="F55" s="174"/>
+      <c r="G55" s="174"/>
     </row>
     <row r="56" spans="1:7" ht="18">
       <c r="A56" s="71"/>
@@ -27013,28 +27887,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="175" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="178"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -28041,15 +28915,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="175" t="s">
+      <c r="A55" s="174" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="175"/>
-      <c r="C55" s="175"/>
-      <c r="D55" s="175"/>
-      <c r="E55" s="175"/>
-      <c r="F55" s="175"/>
-      <c r="G55" s="175"/>
+      <c r="B55" s="174"/>
+      <c r="C55" s="174"/>
+      <c r="D55" s="174"/>
+      <c r="E55" s="174"/>
+      <c r="F55" s="174"/>
+      <c r="G55" s="174"/>
     </row>
     <row r="56" spans="1:7" ht="18">
       <c r="A56" s="71"/>
@@ -28084,28 +28958,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="175" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="178"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -29113,15 +29987,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="175" t="s">
+      <c r="A55" s="174" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="175"/>
-      <c r="C55" s="175"/>
-      <c r="D55" s="175"/>
-      <c r="E55" s="175"/>
-      <c r="F55" s="175"/>
-      <c r="G55" s="175"/>
+      <c r="B55" s="174"/>
+      <c r="C55" s="174"/>
+      <c r="D55" s="174"/>
+      <c r="E55" s="174"/>
+      <c r="F55" s="174"/>
+      <c r="G55" s="174"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -29154,28 +30028,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="175" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="178"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -30341,28 +31215,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="167" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="178"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174" t="s">
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
